--- a/docs/非凸α-接口总表.xlsx
+++ b/docs/非凸α-接口总表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口总表" sheetId="1" r:id="Rc8063e171f93470e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口总表" sheetId="1" r:id="Rc1aa8081fad1487a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -240,7 +240,6 @@
       <x:c r="P1" t="str">
         <x:v>source_path</x:v>
       </x:c>
-      <x:c r="Q1" t="str"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -291,7 +290,6 @@
       <x:c r="P2" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/run_single_lio.sh</x:v>
       </x:c>
-      <x:c r="Q2" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -342,7 +340,6 @@
       <x:c r="P3" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/run_single_vio.sh</x:v>
       </x:c>
-      <x:c r="Q3" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -393,7 +390,6 @@
       <x:c r="P4" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/takeoff.sh</x:v>
       </x:c>
-      <x:c r="Q4" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
@@ -444,7 +440,6 @@
       <x:c r="P5" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/pub_trigger.sh</x:v>
       </x:c>
-      <x:c r="Q5" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
@@ -495,7 +490,6 @@
       <x:c r="P6" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/back.sh</x:v>
       </x:c>
-      <x:c r="Q6" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
@@ -546,7 +540,6 @@
       <x:c r="P7" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/land.sh</x:v>
       </x:c>
-      <x:c r="Q7" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
@@ -568,36 +561,33 @@
         <x:v>quadrotor_msgs/TakeoffLand</x:v>
       </x:c>
       <x:c r="G8" t="str">
-        <x:v>takeoff_land_cmd={1 takeoff</x:v>
+        <x:v>takeoff_land_cmd={1 takeoff,2 land}</x:v>
       </x:c>
       <x:c r="H8" t="str">
-        <x:v>2 land}</x:v>
+        <x:v>script or RC bridge</x:v>
       </x:c>
       <x:c r="I8" t="str">
-        <x:v>script or RC bridge</x:v>
+        <x:v>px4ctrl</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>px4ctrl</x:v>
+        <x:v>px4ctrl 与定位链正常</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>px4ctrl 与定位链正常</x:v>
+        <x:v>起飞与降落动作原语</x:v>
       </x:c>
       <x:c r="L8" t="str">
-        <x:v>起飞与降落动作原语</x:v>
+        <x:v>rostopic pub -1 /px4ctrl/takeoff_land quadrotor_msgs/TakeoffLand 'takeoff_land_cmd: 1'</x:v>
       </x:c>
       <x:c r="M8" t="str">
-        <x:v>rostopic pub -1 /px4ctrl/takeoff_land quadrotor_msgs/TakeoffLand 'takeoff_land_cmd: 1'</x:v>
+        <x:v>onboard-active</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>onboard-active</x:v>
+        <x:v>RC 档位不对会被拒绝</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>RC 档位不对会被拒绝</x:v>
+        <x:v>E008_takeoff_topic</x:v>
       </x:c>
       <x:c r="P8" t="str">
-        <x:v>E008_takeoff_topic</x:v>
-      </x:c>
-      <x:c r="Q8" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/takeoff.sh</x:v>
       </x:c>
     </x:row>
@@ -650,7 +640,6 @@
       <x:c r="P9" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
-      <x:c r="Q9" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
@@ -701,7 +690,6 @@
       <x:c r="P10" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
-      <x:c r="Q10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
@@ -752,7 +740,6 @@
       <x:c r="P11" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
-      <x:c r="Q11" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
@@ -803,7 +790,6 @@
       <x:c r="P12" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
-      <x:c r="Q12" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
@@ -854,7 +840,6 @@
       <x:c r="P13" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/realflight_modules/px4ctrl/launch/run_ctrl_lio.launch</x:v>
       </x:c>
-      <x:c r="Q13" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -905,7 +890,6 @@
       <x:c r="P14" t="str">
         <x:v>uav/10-knowledge-base/06-指令速查-含隐藏命令.md</x:v>
       </x:c>
-      <x:c r="Q14" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
@@ -956,7 +940,6 @@
       <x:c r="P15" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
-      <x:c r="Q15" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
@@ -1007,7 +990,6 @@
       <x:c r="P16" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
-      <x:c r="Q16" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
@@ -1058,7 +1040,6 @@
       <x:c r="P17" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/realflight_modules/px4ctrl/src/px4ctrl_node.cpp</x:v>
       </x:c>
-      <x:c r="Q17" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
@@ -1109,7 +1090,6 @@
       <x:c r="P18" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
-      <x:c r="Q18" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
@@ -1160,7 +1140,6 @@
       <x:c r="P19" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
-      <x:c r="Q19" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
@@ -1211,7 +1190,6 @@
       <x:c r="P20" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
-      <x:c r="Q20" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
@@ -1262,7 +1240,6 @@
       <x:c r="P21" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
-      <x:c r="Q21" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
@@ -1313,7 +1290,6 @@
       <x:c r="P22" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
-      <x:c r="Q22" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
@@ -1364,7 +1340,6 @@
       <x:c r="P23" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/diff_planner/plan_manage/launch/exp/run_exp_single_lio.launch</x:v>
       </x:c>
-      <x:c r="Q23" t="str"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
@@ -1415,7 +1390,6 @@
       <x:c r="P24" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/config/points.yaml</x:v>
       </x:c>
-      <x:c r="Q24" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
@@ -1466,7 +1440,6 @@
       <x:c r="P25" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/realflight_modules/px4ctrl/config/ctrl_param_fpv.yaml</x:v>
       </x:c>
-      <x:c r="Q25" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
@@ -1517,7 +1490,6 @@
       <x:c r="P26" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/launch/multipointplan_exp_lio.launch</x:v>
       </x:c>
-      <x:c r="Q26" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
@@ -1568,7 +1540,6 @@
       <x:c r="P27" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/diff_planner/plan_manage/launch/exp/run_exp_single_lio.launch</x:v>
       </x:c>
-      <x:c r="Q27" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
@@ -1619,7 +1590,6 @@
       <x:c r="P28" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/diff_planner/plan_manage/launch/exp/run_exp_single_vio.launch</x:v>
       </x:c>
-      <x:c r="Q28" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
@@ -1670,7 +1640,6 @@
       <x:c r="P29" t="str">
         <x:v>uav/10-knowledge-base/01-硬件与系统.md</x:v>
       </x:c>
-      <x:c r="Q29" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
@@ -1721,7 +1690,6 @@
       <x:c r="P30" t="str">
         <x:v>uav/10-knowledge-base/01-硬件与系统.md</x:v>
       </x:c>
-      <x:c r="Q30" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
@@ -1772,7 +1740,6 @@
       <x:c r="P31" t="str">
         <x:v>uav/10-knowledge-base/01-硬件与系统.md</x:v>
       </x:c>
-      <x:c r="Q31" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
@@ -1823,7 +1790,6 @@
       <x:c r="P32" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
-      <x:c r="Q32" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/非凸α-接口总表.xlsx
+++ b/docs/非凸α-接口总表.xlsx
@@ -2,7 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口总表" sheetId="1" r:id="Rc1aa8081fad1487a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怎么用" sheetId="1" r:id="Ra41a9c1533b7407a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推荐接入" sheetId="2" r:id="Rdc822cbeadd74d22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景速查" sheetId="3" r:id="Rb8201ccd420341c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态接口" sheetId="4" r:id="R8ae0a3964de547fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动作接口" sheetId="5" r:id="Rd3bf4f78572342c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="脚本入口" sheetId="6" r:id="R8a01bfedcd134888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数入口" sheetId="7" r:id="R3391b74b58484825"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RC映射" sheetId="8" r:id="R523e810ac0f84000"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整原表" sheetId="9" r:id="Ra74cd0e5f3694c7c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,28 +21,156 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color theme="0"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="444444"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="0"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4" tint="0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="5" tint="0.35"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="9">
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -190,1604 +326,3437 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="25.149999618530273" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="43.560001373291016" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="str">
+      <x:c r="A1" s="2" t="str">
+        <x:v>非凸α接口总表怎么用</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这份表不是让你逐行背。先看“推荐接入”，再按任务去看状态接口、动作接口、脚本入口、参数入口和 RC 映射，最后才看完整原表。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>先按你的问题去找 sheet</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>我现在要做什么</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>先看哪个 sheet</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>为什么</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>不想按类别读，想按任务场景直接找</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>场景速查</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>把日常最常见的开发和排查场景压成一张表，先看这里最快。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>判断上层系统先接哪些接口</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>推荐接入</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>这里把当前机器最值得先订阅和先发布的接口浓缩好了。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>看电量、状态、定位</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>状态接口</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>这是日常观测入口，先订阅这些再谈上层逻辑。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>触发起飞、开始任务、返程、降落</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>动作接口</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>这些是当前机器已经稳定落地的动作原语。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>搞清楚一键脚本到底起了什么</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>脚本入口</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>这里把 run_single_lio/vio 和动作脚本拆开写了。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>想改航点、起飞高度、规划参数</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>参数入口</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>这里告诉你该改哪个文件，不用翻整仓。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>想确认遥控器会不会打断软件</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>RC映射</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>RC 是最高优先级安全边界，这里单独列出。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="15" t="str">
+        <x:v>要追溯到原始事实</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="str">
+        <x:v>完整原表</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:v>保留全部字段，便于追源码和证据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="6" t="str">
+        <x:v>给上层系统的最小闭环</x:v>
+      </x:c>
+      <x:c r="B16" s="6"/>
+      <x:c r="C16" s="6"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="9" t="str">
+        <x:v>目标</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="str">
+        <x:v>推荐接口</x:v>
+      </x:c>
+      <x:c r="C17" s="9" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
+        <x:v>状态订阅</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="str">
+        <x:v>/mavros/state, /mavros/battery, /mavros/rc/in</x:v>
+      </x:c>
+      <x:c r="C18" s="12" t="str">
+        <x:v>先拿到飞控、供电和 RC 安全门，别一上来就发控制。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="13" t="str">
+        <x:v>定位订阅</x:v>
+      </x:c>
+      <x:c r="B19" s="3" t="str">
+        <x:v>/ekf/ekf_odom 或 /vins/imu_propagate</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str">
+        <x:v>LIO/VIO 二选一，根据当前启动链决定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="13" t="str">
+        <x:v>动作发布</x:v>
+      </x:c>
+      <x:c r="B20" s="3" t="str">
+        <x:v>/px4ctrl/takeoff_land, /move_base_simple/goal, /back_trigger</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="str">
+        <x:v>这是当前机器最适合上层系统直接调用的动作层。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="15" t="str">
+        <x:v>先别碰</x:v>
+      </x:c>
+      <x:c r="B21" s="16" t="str">
+        <x:v>/setpoints_cmd 和 px4ctrl 内部状态机</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="str">
+        <x:v>这两层风险更高，不适合作为第一接入点。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="31.290000915527344" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>推荐接入</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>如果你要做二开，先围绕这 8 个接口建立闭环，不要第一步就下钻到控制器内部。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>建议你先围绕这些接口做开发</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>接入目标</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>接口</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>类型</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>方向</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>怎么用</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>前置条件</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="str">
+        <x:v>风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>看飞控连接与模式</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>/mavros/state</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>查看飞控连接与模式</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>mavros 已启动</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str">
+        <x:v>最先判断 FCU 是否连上</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>看电量</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>/mavros/battery</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>查看电量</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="str">
+        <x:v>mavros 已启动</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
+        <x:v>低压阈值与 ctrl_param_fpv.yaml 联动</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>看 RC 安全门</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>/mavros/rc/in</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>查看遥控器输入</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="str">
+        <x:v>mavros 已启动且 RC 在线</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>是安全门也是动作触发来源</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>看 LIO 定位</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>/ekf/ekf_odom</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>查看融合 odom</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="str">
+        <x:v>LIO 主链已启动</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>LIO 主链下的核心定位输出</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>看 VIO 定位</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>/vins/imu_propagate</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>查看视觉惯性 odom</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
+        <x:v>VIO 主链已启动</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>当前视觉定位主输出</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>触发起飞/降落</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>/px4ctrl/takeoff_land</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>起飞与降落动作原语</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
+        <x:v>px4ctrl 与定位链正常</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>RC 档位不对会被拒绝</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>触发开始任务</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>/move_base_simple/goal</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>开始执行点位任务</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
+        <x:v>multipoint 启动且 start_plan=1</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>不要和 RC 八通重复发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="15" t="str">
+        <x:v>触发返程</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="str">
+        <x:v>/back_trigger</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="str">
+        <x:v>开始返程任务</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="str">
+        <x:v>multipoint 启动且 back_plan=1</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="str">
+        <x:v>返回路径依赖 test_back</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="17.790000915527344" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28.829999923706055" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="31.290000915527344" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>场景速查</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>如果你已经知道自己要做什么，就先从这一页进，不要先扎进完整原表。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>按场景找入口</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>先做什么</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>关键接口/文件</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>深挖去哪</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>看电量</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>先确认 mavros 在线</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>/mavros/battery</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>状态接口</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="str">
+        <x:v>最常用日常检查项，先看电压和 percentage。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>看飞控状态</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>先看连接、armed、mode</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>/mavros/state</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>状态接口</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>起飞前和排障时都应先看它。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>看定位是否正常</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>按当前启动链选 LIO 或 VIO</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>/ekf/ekf_odom 或 /vins/imu_propagate</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>状态接口</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>LIO/VIO 二选一，不要混着判断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>看 RC 会不会打断软件</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>先看原始通道，再看通道含义</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>/mavros/rc/in + RC Channel 5/6/7/8</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>RC映射</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>RC 是最高优先级安全边界。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>触发起飞</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>确认前置条件后再发动作</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>/px4ctrl/takeoff_land 或 takeoff.sh</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>动作接口 / 脚本入口</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>takeoff_land_cmd=1；RC 档位不对时会被拒绝。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>开始任务</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>触发任务入口，不直接发底层控制</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>/move_base_simple/goal 或 pub_trigger.sh</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>动作接口 / 脚本入口</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>当前多点任务最自然的开始入口。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>返程</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>走返程 trigger，不要直接猜返回点逻辑</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>/back_trigger 或 back.sh</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>动作接口 / 脚本入口</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>具体返程点来自 points.yaml 里的 test_back。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>降落</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="str">
+        <x:v>优先用已有动作原语</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>/px4ctrl/takeoff_land 或 land.sh</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>动作接口 / 脚本入口</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>takeoff_land_cmd=2；与起飞共用同一 topic。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>改航点</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="str">
+        <x:v>先改 YAML，再确认模式</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>points.yaml + multipointplan_exp_lio.launch</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="str">
+        <x:v>参数入口</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>先确认 fligt_type，再按 test1~test4 格式改。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>改起飞高度</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="str">
+        <x:v>只改控制器参数，不要误改规划参数</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="str">
+        <x:v>ctrl_param_fpv.yaml</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="str">
+        <x:v>参数入口</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="str">
+        <x:v>对应 auto_takeoff_land.takeoff_height。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="15" t="str">
+        <x:v>接上层 Agent / MQTT</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
+        <x:v>先做状态订阅和动作发布闭环</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="str">
+        <x:v>/mavros/state, /mavros/battery, /px4ctrl/takeoff_land, /move_base_simple/goal</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="str">
+        <x:v>推荐接入</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="str">
+        <x:v>第一刀不要碰 /setpoints_cmd 和 px4ctrl 状态机。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.109999656677246" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>状态接口</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>日常观察先从这里开始。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+      <x:c r="H2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>当前最常用的状态类接口</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>接口</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>消息类型</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>上游</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>下游/使用者</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>用途</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>常用命令</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="str">
+        <x:v>风险/备注</x:v>
+      </x:c>
+      <x:c r="H5" s="9" t="str">
+        <x:v>当前状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>/mavros/state</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>mavros_msgs/State</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>mavros</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>operator / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>查看飞控连接与模式</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>rostopic echo -n 1 /mavros/state</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>最先判断 FCU 是否连上</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>/mavros/battery</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>sensor_msgs/BatteryState</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>mavros</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>operator / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>查看电量</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="str">
+        <x:v>rostopic echo -n 1 /mavros/battery</x:v>
+      </x:c>
+      <x:c r="G7" s="3" t="str">
+        <x:v>低压阈值与 ctrl_param_fpv.yaml 联动</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>/mavros/rc/in</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>mavros_msgs/RCIn</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>mavros</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>multipoint / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>查看遥控器输入</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="str">
+        <x:v>rostopic echo -n 1 /mavros/rc/in</x:v>
+      </x:c>
+      <x:c r="G8" s="3" t="str">
+        <x:v>是安全门也是动作触发来源</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>/mavros/imu/data</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>sensor_msgs/Imu</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>mavros</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>px4ctrl</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>飞控 IMU 输入</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="str">
+        <x:v>rostopic echo -n 1 /mavros/imu/data</x:v>
+      </x:c>
+      <x:c r="G9" s="3" t="str">
+        <x:v>px4ctrl 明确使用 data 非 data_raw</x:v>
+      </x:c>
+      <x:c r="H9" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>/mavros/local_position/pose</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>mavros</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>operator</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>查看 PX4 本地位姿</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
+        <x:v>rostopic echo -n 1 /mavros/local_position/pose</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="str">
+        <x:v>与机载 EKF 输出不同源</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>/ekf/ekf_odom</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>nav_msgs/Odometry</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>ekf</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>planner / operator</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>查看融合 odom</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
+        <x:v>rostopic echo -n 1 /ekf/ekf_odom</x:v>
+      </x:c>
+      <x:c r="G11" s="3" t="str">
+        <x:v>LIO 主链下的核心定位输出</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>/laserMapping/odometry</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>nav_msgs/Odometry</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>faster_lio</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>ekf / operator</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>查看雷达 odom</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
+        <x:v>rostopic echo -n 1 /laserMapping/odometry</x:v>
+      </x:c>
+      <x:c r="G12" s="3" t="str">
+        <x:v>ekf 会依赖它</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>/laserMapping/cloud_registered</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="str">
+        <x:v>sensor_msgs/PointCloud2</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>faster_lio</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>planner / rviz</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
+        <x:v>查看规划输入点云</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="str">
+        <x:v>rostopic hz /laserMapping/cloud_registered</x:v>
+      </x:c>
+      <x:c r="G13" s="3" t="str">
+        <x:v>rviz 观察质量时重点看它</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>/vins/imu_propagate</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="str">
+        <x:v>nav_msgs/Odometry</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>vins</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="str">
+        <x:v>planner / operator</x:v>
+      </x:c>
+      <x:c r="E14" s="3" t="str">
+        <x:v>查看视觉惯性 odom</x:v>
+      </x:c>
+      <x:c r="F14" s="3" t="str">
+        <x:v>rostopic echo -n 1 /vins/imu_propagate</x:v>
+      </x:c>
+      <x:c r="G14" s="3" t="str">
+        <x:v>当前视觉定位主输出</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="15" t="str">
+        <x:v>/drone_0_planning/trajectory</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="str">
+        <x:v>traj_utils/PolyTraj</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="str">
+        <x:v>traj_server</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="str">
+        <x:v>operator / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="str">
+        <x:v>查看当前规划结果</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="str">
+        <x:v>rostopic echo -n 1 /drone_0_planning/trajectory</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="str">
+        <x:v>轨迹有了不等于控制器一定执行</x:v>
+      </x:c>
+      <x:c r="H15" s="17" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23.93000030517578" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28.829999923706055" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28.829999923706055" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>动作接口</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这是当前机器最适合上层系统直接调用的动作原语层。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>动作接口</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>接口</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>输入格式</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>方向</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>前置条件</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>作用</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="str">
+        <x:v>风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>/px4ctrl/takeoff_land</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>quadrotor_msgs/TakeoffLand</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>px4ctrl 与定位链正常</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>起飞与降落动作原语</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>rostopic pub -1 /px4ctrl/takeoff_land quadrotor_msgs/TakeoffLand 'takeoff_land_cmd: 1'</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str">
+        <x:v>RC 档位不对会被拒绝</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>/move_base_simple/goal</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>multipoint 启动且 start_plan=1</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>开始执行点位任务</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="str">
+        <x:v>rostopic pub -1 /move_base_simple/goal geometry_msgs/PoseStamped '{}'</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
+        <x:v>不要和 RC 八通重复发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>/back_trigger</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>multipoint 启动且 back_plan=1</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>开始返程任务</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="str">
+        <x:v>rostopic pub -1 /back_trigger geometry_msgs/PoseStamped '{}'</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>返回路径依赖 test_back</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>/goal</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>任务已启动</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>逐个向规划器发目标点</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="str">
+        <x:v>由 multipoint 自动发布</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>通常不建议外部直接绕过 multipoint 写它</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>/planning/yaw</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>quadrotor_msgs/PositionCommand</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>使用 test3 或 test4</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>按航点注入 yaw</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
+        <x:v>由 multipoint 自动发布</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>VIO 模式不建议使用自定义 yaw</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="15" t="str">
+        <x:v>/setpoints_cmd</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="str">
+        <x:v>quadrotor_msgs/PositionCommand</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="str">
+        <x:v>planner 与 px4ctrl 同时存在</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="str">
+        <x:v>规划器给控制器的核心命令通道</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="str">
+        <x:v>内部 remap 到 /setpoints_cmd</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="str">
+        <x:v>高风险接口 不要先从这里直接接上层系统</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="31.290000915527344" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28.829999923706055" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>脚本入口</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>现场同事真实在用的是脚本入口，这里告诉你每个脚本大致负责什么。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>脚本入口</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>脚本</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>类型/格式</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>关键内容</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>前置条件</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>典型用途</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>run_single_lio.sh</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>bash script</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>mavros, faster_lio, ekf, planner, px4ctrl, multipoint</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>Diff-planner workspace sourced</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>启动单机 LIO 全栈</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>启动慢时不要误判失败</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>run_single_vio.sh</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>bash script</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>mavros, realsense, vins, planner, px4ctrl, multipoint</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>Diff-planner workspace sourced</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>启动单机 VIO 全栈</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>相机起不来时 VIO 全链失效</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>takeoff.sh</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>rostopic pub -1 quadrotor_msgs/TakeoffLand</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>takeoff_land_cmd=1</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>px4ctrl 已启动</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>触发自动起飞</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>RC 状态不满足时 px4ctrl 会拒绝</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>pub_trigger.sh</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>rostopic pub -1 geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>empty pose trigger</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>multipoint 已启动</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>触发开始任务</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>不要与 8 通上拨重复触发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>back.sh</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>rostopic pub -1 geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>empty pose trigger</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>multipoint 已启动</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>触发返程</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>不要与 8 通中拨重复触发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="15" t="str">
+        <x:v>land.sh</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="str">
+        <x:v>rostopic pub -1 quadrotor_msgs/TakeoffLand</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="str">
+        <x:v>takeoff_land_cmd=2</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="str">
+        <x:v>px4ctrl 已启动</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="str">
+        <x:v>触发自动降落</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="str">
+        <x:v>与 takeoff.sh 共用同一 topic</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23.93000030517578" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23.93000030517578" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28.829999923706055" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>参数入口</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>如果你是来改行为，不是来重写系统，那先看这些文件。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>参数入口</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>文件</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>格式</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>关键参数</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>作用</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>典型用法</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>points.yaml</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>yaml</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>test1 test2 test3 test4 test_back</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>定义任务点和返程点</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>src/user_command/multipoint/config/points.yaml</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>数组长度错会直接读取失败</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>ctrl_param_fpv.yaml</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>yaml</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>low_voltage takeoff_height takeoff_land_speed</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>控制起飞高度和电池阈值</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>src/realflight_modules/px4ctrl/config/ctrl_param_fpv.yaml</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>改前必须确认起飞高度范围无障碍</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>multipointplan_exp_lio.launch</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>roslaunch args</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>fligt_type next_distance start_plan back_plan</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>选择航点模式和触发行为</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>roslaunch multipoint multipointplan_exp_lio.launch</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>fligt_type 拼写就是源码现状 不要擅自改名</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>run_exp_single_lio.launch</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>roslaunch args</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>max_vel max_acc map_resolution flight_type</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>配置 LIO 规划参数</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>roslaunch diff_planner run_exp_single_lio.launch</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>是规划参数不是飞控参数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="15" t="str">
+        <x:v>run_exp_single_vio.launch</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="str">
+        <x:v>roslaunch args</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="str">
+        <x:v>cx cy fx fy max_vel max_acc</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="str">
+        <x:v>配置 VIO 规划参数</x:v>
+      </x:c>
+      <x:c r="E10" s="16" t="str">
+        <x:v>roslaunch diff_planner run_exp_single_vio.launch</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="str">
+        <x:v>视觉内参错误会直接破坏 VIO 规划</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15.34000015258789" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23.93000030517578" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28.829999923706055" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>RC映射</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>开发时一定要把 RC 当作安全边界，而不是背景信息。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>遥控器映射</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>通道</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>输入类型</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>含义</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>下游</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>典型用途</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>RC Channel 5</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>remote control</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>光流 / 姿态 / onboard</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>PX4 / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>切换飞行模式</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>软件控制会被它打断</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>RC Channel 6</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>remote control</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>悬停 / 轨迹</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>PX4 / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>切换悬停与轨迹控制</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>异常时上拨 6 通是重要兜底</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>RC Channel 7</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>remote control</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>解锁 / 锁桨 / 急停</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>PX4</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>电机安全控制</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>最高安全优先级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="15" t="str">
+        <x:v>RC Channel 8</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>remote control</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>下-&gt;中 takeoff 中-&gt;上 start 上-&gt;中 back 中-&gt;下 land</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="str">
+        <x:v>multipoint / PX4</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="str">
+        <x:v>任务动作触发</x:v>
+      </x:c>
+      <x:c r="F9" s="17" t="str">
+        <x:v>脚本与 RC 触发方式不要混用</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9.199999809265137" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.65999984741211" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="19.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="31.290000915527344" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>完整原表</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
+      <x:c r="J1" s="2"/>
+      <x:c r="K1" s="2"/>
+      <x:c r="L1" s="2"/>
+      <x:c r="M1" s="2"/>
+      <x:c r="N1" s="2"/>
+      <x:c r="O1" s="2"/>
+      <x:c r="P1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这里保留全部原始字段，用于追溯和查证。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+      <x:c r="H2" s="4"/>
+      <x:c r="I2" s="4"/>
+      <x:c r="J2" s="4"/>
+      <x:c r="K2" s="4"/>
+      <x:c r="L2" s="4"/>
+      <x:c r="M2" s="4"/>
+      <x:c r="N2" s="4"/>
+      <x:c r="O2" s="4"/>
+      <x:c r="P2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>完整原表</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
+      <x:c r="I4" s="6"/>
+      <x:c r="J4" s="6"/>
+      <x:c r="K4" s="6"/>
+      <x:c r="L4" s="6"/>
+      <x:c r="M4" s="6"/>
+      <x:c r="N4" s="6"/>
+      <x:c r="O4" s="6"/>
+      <x:c r="P4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B1" t="str">
+      <x:c r="B5" s="9" t="str">
         <x:v>category</x:v>
       </x:c>
-      <x:c r="C1" t="str">
+      <x:c r="C5" s="9" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>type</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="E5" s="9" t="str">
         <x:v>direction</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="F5" s="9" t="str">
         <x:v>message_or_format</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="G5" s="9" t="str">
         <x:v>key_fields</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="H5" s="9" t="str">
         <x:v>upstream</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="I5" s="9" t="str">
         <x:v>downstream</x:v>
       </x:c>
-      <x:c r="J1" t="str">
+      <x:c r="J5" s="9" t="str">
         <x:v>preconditions</x:v>
       </x:c>
-      <x:c r="K1" t="str">
+      <x:c r="K5" s="9" t="str">
         <x:v>typical_use</x:v>
       </x:c>
-      <x:c r="L1" t="str">
+      <x:c r="L5" s="9" t="str">
         <x:v>example</x:v>
       </x:c>
-      <x:c r="M1" t="str">
+      <x:c r="M5" s="9" t="str">
         <x:v>machine_status</x:v>
       </x:c>
-      <x:c r="N1" t="str">
+      <x:c r="N5" s="9" t="str">
         <x:v>risks</x:v>
       </x:c>
-      <x:c r="O1" t="str">
+      <x:c r="O5" s="9" t="str">
         <x:v>evidence_id</x:v>
       </x:c>
-      <x:c r="P1" t="str">
+      <x:c r="P5" s="9" t="str">
         <x:v>source_path</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
         <x:v>I001</x:v>
       </x:c>
-      <x:c r="B2" t="str">
+      <x:c r="B6" s="11" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C2" t="str">
+      <x:c r="C6" s="11" t="str">
         <x:v>run_single_lio.sh</x:v>
       </x:c>
-      <x:c r="D2" t="str">
+      <x:c r="D6" s="11" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E2" t="str">
+      <x:c r="E6" s="11" t="str">
         <x:v>entrypoint</x:v>
       </x:c>
-      <x:c r="F2" t="str">
+      <x:c r="F6" s="11" t="str">
         <x:v>bash script</x:v>
       </x:c>
-      <x:c r="G2" t="str">
+      <x:c r="G6" s="11" t="str">
         <x:v>mavros, faster_lio, ekf, planner, px4ctrl, multipoint</x:v>
       </x:c>
-      <x:c r="H2" t="str">
+      <x:c r="H6" s="11" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I2" t="str">
+      <x:c r="I6" s="11" t="str">
         <x:v>ROS graph</x:v>
       </x:c>
-      <x:c r="J2" t="str">
+      <x:c r="J6" s="11" t="str">
         <x:v>Diff-planner workspace sourced</x:v>
       </x:c>
-      <x:c r="K2" t="str">
+      <x:c r="K6" s="11" t="str">
         <x:v>启动单机 LIO 全栈</x:v>
       </x:c>
-      <x:c r="L2" t="str">
-        <x:v>cd ~/Diff-Planner &amp;&amp; ./sh_files/run_single_lio.sh</x:v>
-      </x:c>
-      <x:c r="M2" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N2" t="str">
+      <x:c r="L6" s="11" t="str">
+        <x:v>cd ~/Diff-planner &amp;&amp; ./sh_files/run_single_lio.sh</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N6" s="11" t="str">
         <x:v>启动慢时不要误判失败</x:v>
       </x:c>
-      <x:c r="O2" t="str">
+      <x:c r="O6" s="11" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
-      <x:c r="P2" t="str">
+      <x:c r="P6" s="12" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/run_single_lio.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
         <x:v>I002</x:v>
       </x:c>
-      <x:c r="B3" t="str">
+      <x:c r="B7" s="3" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C3" t="str">
+      <x:c r="C7" s="3" t="str">
         <x:v>run_single_vio.sh</x:v>
       </x:c>
-      <x:c r="D3" t="str">
+      <x:c r="D7" s="3" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E3" t="str">
+      <x:c r="E7" s="3" t="str">
         <x:v>entrypoint</x:v>
       </x:c>
-      <x:c r="F3" t="str">
+      <x:c r="F7" s="3" t="str">
         <x:v>bash script</x:v>
       </x:c>
-      <x:c r="G3" t="str">
+      <x:c r="G7" s="3" t="str">
         <x:v>mavros, realsense, vins, planner, px4ctrl, multipoint</x:v>
       </x:c>
-      <x:c r="H3" t="str">
+      <x:c r="H7" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I3" t="str">
+      <x:c r="I7" s="3" t="str">
         <x:v>ROS graph</x:v>
       </x:c>
-      <x:c r="J3" t="str">
+      <x:c r="J7" s="3" t="str">
         <x:v>Diff-planner workspace sourced</x:v>
       </x:c>
-      <x:c r="K3" t="str">
+      <x:c r="K7" s="3" t="str">
         <x:v>启动单机 VIO 全栈</x:v>
       </x:c>
-      <x:c r="L3" t="str">
-        <x:v>cd ~/Diff-Planner &amp;&amp; ./sh_files/run_single_vio.sh</x:v>
-      </x:c>
-      <x:c r="M3" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N3" t="str">
+      <x:c r="L7" s="3" t="str">
+        <x:v>cd ~/Diff-planner &amp;&amp; ./sh_files/run_single_vio.sh</x:v>
+      </x:c>
+      <x:c r="M7" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N7" s="3" t="str">
         <x:v>相机起不来时 VIO 全链失效</x:v>
       </x:c>
-      <x:c r="O3" t="str">
+      <x:c r="O7" s="3" t="str">
         <x:v>E007_run_single_vio_script</x:v>
       </x:c>
-      <x:c r="P3" t="str">
+      <x:c r="P7" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/run_single_vio.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
         <x:v>I003</x:v>
       </x:c>
-      <x:c r="B4" t="str">
+      <x:c r="B8" s="3" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C4" t="str">
+      <x:c r="C8" s="3" t="str">
         <x:v>takeoff.sh</x:v>
       </x:c>
-      <x:c r="D4" t="str">
+      <x:c r="D8" s="3" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E4" t="str">
+      <x:c r="E8" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F4" t="str">
+      <x:c r="F8" s="3" t="str">
         <x:v>rostopic pub -1 quadrotor_msgs/TakeoffLand</x:v>
       </x:c>
-      <x:c r="G4" t="str">
+      <x:c r="G8" s="3" t="str">
         <x:v>takeoff_land_cmd=1</x:v>
       </x:c>
-      <x:c r="H4" t="str">
+      <x:c r="H8" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I4" t="str">
+      <x:c r="I8" s="3" t="str">
         <x:v>/px4ctrl/takeoff_land</x:v>
       </x:c>
-      <x:c r="J4" t="str">
+      <x:c r="J8" s="3" t="str">
         <x:v>px4ctrl 已启动</x:v>
       </x:c>
-      <x:c r="K4" t="str">
+      <x:c r="K8" s="3" t="str">
         <x:v>触发自动起飞</x:v>
       </x:c>
-      <x:c r="L4" t="str">
+      <x:c r="L8" s="3" t="str">
         <x:v>./sh_files/takeoff.sh</x:v>
       </x:c>
-      <x:c r="M4" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N4" t="str">
+      <x:c r="M8" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N8" s="3" t="str">
         <x:v>RC 状态不满足时 px4ctrl 会拒绝</x:v>
       </x:c>
-      <x:c r="O4" t="str">
+      <x:c r="O8" s="3" t="str">
         <x:v>E008_takeoff_topic</x:v>
       </x:c>
-      <x:c r="P4" t="str">
+      <x:c r="P8" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/takeoff.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
         <x:v>I004</x:v>
       </x:c>
-      <x:c r="B5" t="str">
+      <x:c r="B9" s="3" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C5" t="str">
+      <x:c r="C9" s="3" t="str">
         <x:v>pub_trigger.sh</x:v>
       </x:c>
-      <x:c r="D5" t="str">
+      <x:c r="D9" s="3" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E5" t="str">
+      <x:c r="E9" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F5" t="str">
+      <x:c r="F9" s="3" t="str">
         <x:v>rostopic pub -1 geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G5" t="str">
+      <x:c r="G9" s="3" t="str">
         <x:v>empty pose trigger</x:v>
       </x:c>
-      <x:c r="H5" t="str">
+      <x:c r="H9" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I5" t="str">
+      <x:c r="I9" s="3" t="str">
         <x:v>/move_base_simple/goal</x:v>
       </x:c>
-      <x:c r="J5" t="str">
+      <x:c r="J9" s="3" t="str">
         <x:v>multipoint 已启动</x:v>
       </x:c>
-      <x:c r="K5" t="str">
+      <x:c r="K9" s="3" t="str">
         <x:v>触发开始任务</x:v>
       </x:c>
-      <x:c r="L5" t="str">
+      <x:c r="L9" s="3" t="str">
         <x:v>./sh_files/pub_trigger.sh</x:v>
       </x:c>
-      <x:c r="M5" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N5" t="str">
+      <x:c r="M9" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N9" s="3" t="str">
         <x:v>不要与 8 通上拨重复触发</x:v>
       </x:c>
-      <x:c r="O5" t="str">
+      <x:c r="O9" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P5" t="str">
+      <x:c r="P9" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/pub_trigger.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
         <x:v>I005</x:v>
       </x:c>
-      <x:c r="B6" t="str">
+      <x:c r="B10" s="3" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C6" t="str">
+      <x:c r="C10" s="3" t="str">
         <x:v>back.sh</x:v>
       </x:c>
-      <x:c r="D6" t="str">
+      <x:c r="D10" s="3" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E6" t="str">
+      <x:c r="E10" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F6" t="str">
+      <x:c r="F10" s="3" t="str">
         <x:v>rostopic pub -1 geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G6" t="str">
+      <x:c r="G10" s="3" t="str">
         <x:v>empty pose trigger</x:v>
       </x:c>
-      <x:c r="H6" t="str">
+      <x:c r="H10" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I6" t="str">
+      <x:c r="I10" s="3" t="str">
         <x:v>/back_trigger</x:v>
       </x:c>
-      <x:c r="J6" t="str">
+      <x:c r="J10" s="3" t="str">
         <x:v>multipoint 已启动</x:v>
       </x:c>
-      <x:c r="K6" t="str">
+      <x:c r="K10" s="3" t="str">
         <x:v>触发返程</x:v>
       </x:c>
-      <x:c r="L6" t="str">
+      <x:c r="L10" s="3" t="str">
         <x:v>./sh_files/back.sh</x:v>
       </x:c>
-      <x:c r="M6" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N6" t="str">
+      <x:c r="M10" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N10" s="3" t="str">
         <x:v>不要与 8 通中拨重复触发</x:v>
       </x:c>
-      <x:c r="O6" t="str">
+      <x:c r="O10" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P6" t="str">
+      <x:c r="P10" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/back.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
         <x:v>I006</x:v>
       </x:c>
-      <x:c r="B7" t="str">
+      <x:c r="B11" s="3" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C7" t="str">
+      <x:c r="C11" s="3" t="str">
         <x:v>land.sh</x:v>
       </x:c>
-      <x:c r="D7" t="str">
+      <x:c r="D11" s="3" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E7" t="str">
+      <x:c r="E11" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F7" t="str">
+      <x:c r="F11" s="3" t="str">
         <x:v>rostopic pub -1 quadrotor_msgs/TakeoffLand</x:v>
       </x:c>
-      <x:c r="G7" t="str">
+      <x:c r="G11" s="3" t="str">
         <x:v>takeoff_land_cmd=2</x:v>
       </x:c>
-      <x:c r="H7" t="str">
+      <x:c r="H11" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I7" t="str">
+      <x:c r="I11" s="3" t="str">
         <x:v>/px4ctrl/takeoff_land</x:v>
       </x:c>
-      <x:c r="J7" t="str">
+      <x:c r="J11" s="3" t="str">
         <x:v>px4ctrl 已启动</x:v>
       </x:c>
-      <x:c r="K7" t="str">
+      <x:c r="K11" s="3" t="str">
         <x:v>触发自动降落</x:v>
       </x:c>
-      <x:c r="L7" t="str">
+      <x:c r="L11" s="3" t="str">
         <x:v>./sh_files/land.sh</x:v>
       </x:c>
-      <x:c r="M7" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N7" t="str">
+      <x:c r="M11" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N11" s="3" t="str">
         <x:v>与 takeoff.sh 共用同一 topic</x:v>
       </x:c>
-      <x:c r="O7" t="str">
+      <x:c r="O11" s="3" t="str">
         <x:v>E008_takeoff_topic</x:v>
       </x:c>
-      <x:c r="P7" t="str">
+      <x:c r="P11" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/land.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
         <x:v>I007</x:v>
       </x:c>
-      <x:c r="B8" t="str">
+      <x:c r="B12" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C8" t="str">
+      <x:c r="C12" s="3" t="str">
         <x:v>/px4ctrl/takeoff_land</x:v>
       </x:c>
-      <x:c r="D8" t="str">
+      <x:c r="D12" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E8" t="str">
+      <x:c r="E12" s="3" t="str">
         <x:v>publish / subscribe</x:v>
       </x:c>
-      <x:c r="F8" t="str">
+      <x:c r="F12" s="3" t="str">
         <x:v>quadrotor_msgs/TakeoffLand</x:v>
       </x:c>
-      <x:c r="G8" t="str">
+      <x:c r="G12" s="3" t="str">
         <x:v>takeoff_land_cmd={1 takeoff,2 land}</x:v>
       </x:c>
-      <x:c r="H8" t="str">
+      <x:c r="H12" s="3" t="str">
         <x:v>script or RC bridge</x:v>
       </x:c>
-      <x:c r="I8" t="str">
+      <x:c r="I12" s="3" t="str">
         <x:v>px4ctrl</x:v>
       </x:c>
-      <x:c r="J8" t="str">
+      <x:c r="J12" s="3" t="str">
         <x:v>px4ctrl 与定位链正常</x:v>
       </x:c>
-      <x:c r="K8" t="str">
+      <x:c r="K12" s="3" t="str">
         <x:v>起飞与降落动作原语</x:v>
       </x:c>
-      <x:c r="L8" t="str">
+      <x:c r="L12" s="3" t="str">
         <x:v>rostopic pub -1 /px4ctrl/takeoff_land quadrotor_msgs/TakeoffLand 'takeoff_land_cmd: 1'</x:v>
       </x:c>
-      <x:c r="M8" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N8" t="str">
+      <x:c r="M12" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N12" s="3" t="str">
         <x:v>RC 档位不对会被拒绝</x:v>
       </x:c>
-      <x:c r="O8" t="str">
+      <x:c r="O12" s="3" t="str">
         <x:v>E008_takeoff_topic</x:v>
       </x:c>
-      <x:c r="P8" t="str">
+      <x:c r="P12" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/takeoff.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
         <x:v>I008</x:v>
       </x:c>
-      <x:c r="B9" t="str">
+      <x:c r="B13" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C9" t="str">
+      <x:c r="C13" s="3" t="str">
         <x:v>/move_base_simple/goal</x:v>
       </x:c>
-      <x:c r="D9" t="str">
+      <x:c r="D13" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E9" t="str">
+      <x:c r="E13" s="3" t="str">
         <x:v>publish / subscribe</x:v>
       </x:c>
-      <x:c r="F9" t="str">
+      <x:c r="F13" s="3" t="str">
         <x:v>geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G9" t="str">
+      <x:c r="G13" s="3" t="str">
         <x:v>header stamp only is sufficient for trigger</x:v>
       </x:c>
-      <x:c r="H9" t="str">
+      <x:c r="H13" s="3" t="str">
         <x:v>script or RC bridge</x:v>
       </x:c>
-      <x:c r="I9" t="str">
+      <x:c r="I13" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="J9" t="str">
+      <x:c r="J13" s="3" t="str">
         <x:v>multipoint 启动且 start_plan=1</x:v>
       </x:c>
-      <x:c r="K9" t="str">
+      <x:c r="K13" s="3" t="str">
         <x:v>开始执行点位任务</x:v>
       </x:c>
-      <x:c r="L9" t="str">
+      <x:c r="L13" s="3" t="str">
         <x:v>rostopic pub -1 /move_base_simple/goal geometry_msgs/PoseStamped '{}'</x:v>
       </x:c>
-      <x:c r="M9" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N9" t="str">
+      <x:c r="M13" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N13" s="3" t="str">
         <x:v>不要和 RC 八通重复发</x:v>
       </x:c>
-      <x:c r="O9" t="str">
+      <x:c r="O13" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P9" t="str">
+      <x:c r="P13" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
         <x:v>I009</x:v>
       </x:c>
-      <x:c r="B10" t="str">
+      <x:c r="B14" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C10" t="str">
+      <x:c r="C14" s="3" t="str">
         <x:v>/back_trigger</x:v>
       </x:c>
-      <x:c r="D10" t="str">
+      <x:c r="D14" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E10" t="str">
+      <x:c r="E14" s="3" t="str">
         <x:v>publish / subscribe</x:v>
       </x:c>
-      <x:c r="F10" t="str">
+      <x:c r="F14" s="3" t="str">
         <x:v>geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G10" t="str">
+      <x:c r="G14" s="3" t="str">
         <x:v>header stamp only is sufficient for trigger</x:v>
       </x:c>
-      <x:c r="H10" t="str">
+      <x:c r="H14" s="3" t="str">
         <x:v>script or RC bridge</x:v>
       </x:c>
-      <x:c r="I10" t="str">
+      <x:c r="I14" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="J10" t="str">
+      <x:c r="J14" s="3" t="str">
         <x:v>multipoint 启动且 back_plan=1</x:v>
       </x:c>
-      <x:c r="K10" t="str">
+      <x:c r="K14" s="3" t="str">
         <x:v>开始返程任务</x:v>
       </x:c>
-      <x:c r="L10" t="str">
+      <x:c r="L14" s="3" t="str">
         <x:v>rostopic pub -1 /back_trigger geometry_msgs/PoseStamped '{}'</x:v>
       </x:c>
-      <x:c r="M10" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N10" t="str">
+      <x:c r="M14" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N14" s="3" t="str">
         <x:v>返回路径依赖 test_back</x:v>
       </x:c>
-      <x:c r="O10" t="str">
+      <x:c r="O14" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P10" t="str">
+      <x:c r="P14" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
         <x:v>I010</x:v>
       </x:c>
-      <x:c r="B11" t="str">
+      <x:c r="B15" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C11" t="str">
+      <x:c r="C15" s="3" t="str">
         <x:v>/goal</x:v>
       </x:c>
-      <x:c r="D11" t="str">
+      <x:c r="D15" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E11" t="str">
+      <x:c r="E15" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F11" t="str">
+      <x:c r="F15" s="3" t="str">
         <x:v>geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G11" t="str">
+      <x:c r="G15" s="3" t="str">
         <x:v>position xyz</x:v>
       </x:c>
-      <x:c r="H11" t="str">
+      <x:c r="H15" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="I11" t="str">
+      <x:c r="I15" s="3" t="str">
         <x:v>planner</x:v>
       </x:c>
-      <x:c r="J11" t="str">
+      <x:c r="J15" s="3" t="str">
         <x:v>任务已启动</x:v>
       </x:c>
-      <x:c r="K11" t="str">
+      <x:c r="K15" s="3" t="str">
         <x:v>逐个向规划器发目标点</x:v>
       </x:c>
-      <x:c r="L11" t="str">
+      <x:c r="L15" s="3" t="str">
         <x:v>由 multipoint 自动发布</x:v>
       </x:c>
-      <x:c r="M11" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N11" t="str">
+      <x:c r="M15" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N15" s="3" t="str">
         <x:v>通常不建议外部直接绕过 multipoint 写它</x:v>
       </x:c>
-      <x:c r="O11" t="str">
+      <x:c r="O15" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P11" t="str">
+      <x:c r="P15" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
         <x:v>I011</x:v>
       </x:c>
-      <x:c r="B12" t="str">
+      <x:c r="B16" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C12" t="str">
+      <x:c r="C16" s="3" t="str">
         <x:v>/planning/yaw</x:v>
       </x:c>
-      <x:c r="D12" t="str">
+      <x:c r="D16" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E12" t="str">
+      <x:c r="E16" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F12" t="str">
+      <x:c r="F16" s="3" t="str">
         <x:v>quadrotor_msgs/PositionCommand</x:v>
       </x:c>
-      <x:c r="G12" t="str">
+      <x:c r="G16" s="3" t="str">
         <x:v>yaw</x:v>
       </x:c>
-      <x:c r="H12" t="str">
+      <x:c r="H16" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="I12" t="str">
+      <x:c r="I16" s="3" t="str">
         <x:v>planner</x:v>
       </x:c>
-      <x:c r="J12" t="str">
+      <x:c r="J16" s="3" t="str">
         <x:v>使用 test3 或 test4</x:v>
       </x:c>
-      <x:c r="K12" t="str">
+      <x:c r="K16" s="3" t="str">
         <x:v>按航点注入 yaw</x:v>
       </x:c>
-      <x:c r="L12" t="str">
+      <x:c r="L16" s="3" t="str">
         <x:v>由 multipoint 自动发布</x:v>
       </x:c>
-      <x:c r="M12" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N12" t="str">
+      <x:c r="M16" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N16" s="3" t="str">
         <x:v>VIO 模式不建议使用自定义 yaw</x:v>
       </x:c>
-      <x:c r="O12" t="str">
+      <x:c r="O16" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P12" t="str">
+      <x:c r="P16" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
         <x:v>I012</x:v>
       </x:c>
-      <x:c r="B13" t="str">
+      <x:c r="B17" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C13" t="str">
+      <x:c r="C17" s="3" t="str">
         <x:v>/setpoints_cmd</x:v>
       </x:c>
-      <x:c r="D13" t="str">
+      <x:c r="D17" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E13" t="str">
+      <x:c r="E17" s="3" t="str">
         <x:v>publish / subscribe</x:v>
       </x:c>
-      <x:c r="F13" t="str">
+      <x:c r="F17" s="3" t="str">
         <x:v>quadrotor_msgs/PositionCommand</x:v>
       </x:c>
-      <x:c r="G13" t="str">
+      <x:c r="G17" s="3" t="str">
         <x:v>position velocity acceleration yaw</x:v>
       </x:c>
-      <x:c r="H13" t="str">
+      <x:c r="H17" s="3" t="str">
         <x:v>traj_server</x:v>
       </x:c>
-      <x:c r="I13" t="str">
+      <x:c r="I17" s="3" t="str">
         <x:v>px4ctrl</x:v>
       </x:c>
-      <x:c r="J13" t="str">
+      <x:c r="J17" s="3" t="str">
         <x:v>planner 与 px4ctrl 同时存在</x:v>
       </x:c>
-      <x:c r="K13" t="str">
+      <x:c r="K17" s="3" t="str">
         <x:v>规划器给控制器的核心命令通道</x:v>
       </x:c>
-      <x:c r="L13" t="str">
+      <x:c r="L17" s="3" t="str">
         <x:v>内部 remap 到 /setpoints_cmd</x:v>
       </x:c>
-      <x:c r="M13" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N13" t="str">
+      <x:c r="M17" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N17" s="3" t="str">
         <x:v>高风险接口 不要先从这里直接接上层系统</x:v>
       </x:c>
-      <x:c r="O13" t="str">
+      <x:c r="O17" s="3" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
-      <x:c r="P13" t="str">
+      <x:c r="P17" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/realflight_modules/px4ctrl/launch/run_ctrl_lio.launch</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
+    <x:row r="18">
+      <x:c r="A18" s="13" t="str">
         <x:v>I013</x:v>
       </x:c>
-      <x:c r="B14" t="str">
+      <x:c r="B18" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C14" t="str">
+      <x:c r="C18" s="3" t="str">
         <x:v>/mavros/state</x:v>
       </x:c>
-      <x:c r="D14" t="str">
+      <x:c r="D18" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E14" t="str">
+      <x:c r="E18" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F14" t="str">
+      <x:c r="F18" s="3" t="str">
         <x:v>mavros_msgs/State</x:v>
       </x:c>
-      <x:c r="G14" t="str">
+      <x:c r="G18" s="3" t="str">
         <x:v>connected armed mode</x:v>
       </x:c>
-      <x:c r="H14" t="str">
+      <x:c r="H18" s="3" t="str">
         <x:v>mavros</x:v>
       </x:c>
-      <x:c r="I14" t="str">
+      <x:c r="I18" s="3" t="str">
         <x:v>operator / px4ctrl</x:v>
       </x:c>
-      <x:c r="J14" t="str">
+      <x:c r="J18" s="3" t="str">
         <x:v>mavros 已启动</x:v>
       </x:c>
-      <x:c r="K14" t="str">
+      <x:c r="K18" s="3" t="str">
         <x:v>查看飞控连接与模式</x:v>
       </x:c>
-      <x:c r="L14" t="str">
+      <x:c r="L18" s="3" t="str">
         <x:v>rostopic echo -n 1 /mavros/state</x:v>
       </x:c>
-      <x:c r="M14" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N14" t="str">
+      <x:c r="M18" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N18" s="3" t="str">
         <x:v>最先判断 FCU 是否连上</x:v>
       </x:c>
-      <x:c r="O14" t="str">
+      <x:c r="O18" s="3" t="str">
         <x:v>E013_battery_topic</x:v>
       </x:c>
-      <x:c r="P14" t="str">
+      <x:c r="P18" s="14" t="str">
         <x:v>uav/10-knowledge-base/06-指令速查-含隐藏命令.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
+    <x:row r="19">
+      <x:c r="A19" s="13" t="str">
         <x:v>I014</x:v>
       </x:c>
-      <x:c r="B15" t="str">
+      <x:c r="B19" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C15" t="str">
+      <x:c r="C19" s="3" t="str">
         <x:v>/mavros/battery</x:v>
       </x:c>
-      <x:c r="D15" t="str">
+      <x:c r="D19" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E15" t="str">
+      <x:c r="E19" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F15" t="str">
+      <x:c r="F19" s="3" t="str">
         <x:v>sensor_msgs/BatteryState</x:v>
       </x:c>
-      <x:c r="G15" t="str">
+      <x:c r="G19" s="3" t="str">
         <x:v>voltage percentage current</x:v>
       </x:c>
-      <x:c r="H15" t="str">
+      <x:c r="H19" s="3" t="str">
         <x:v>mavros</x:v>
       </x:c>
-      <x:c r="I15" t="str">
+      <x:c r="I19" s="3" t="str">
         <x:v>operator / px4ctrl</x:v>
       </x:c>
-      <x:c r="J15" t="str">
+      <x:c r="J19" s="3" t="str">
         <x:v>mavros 已启动</x:v>
       </x:c>
-      <x:c r="K15" t="str">
+      <x:c r="K19" s="3" t="str">
         <x:v>查看电量</x:v>
       </x:c>
-      <x:c r="L15" t="str">
+      <x:c r="L19" s="3" t="str">
         <x:v>rostopic echo -n 1 /mavros/battery</x:v>
       </x:c>
-      <x:c r="M15" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N15" t="str">
+      <x:c r="M19" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N19" s="3" t="str">
         <x:v>低压阈值与 ctrl_param_fpv.yaml 联动</x:v>
       </x:c>
-      <x:c r="O15" t="str">
+      <x:c r="O19" s="3" t="str">
         <x:v>E013_battery_topic</x:v>
       </x:c>
-      <x:c r="P15" t="str">
+      <x:c r="P19" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str">
+    <x:row r="20">
+      <x:c r="A20" s="13" t="str">
         <x:v>I015</x:v>
       </x:c>
-      <x:c r="B16" t="str">
+      <x:c r="B20" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C16" t="str">
+      <x:c r="C20" s="3" t="str">
         <x:v>/mavros/rc/in</x:v>
       </x:c>
-      <x:c r="D16" t="str">
+      <x:c r="D20" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E16" t="str">
+      <x:c r="E20" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F16" t="str">
+      <x:c r="F20" s="3" t="str">
         <x:v>mavros_msgs/RCIn</x:v>
       </x:c>
-      <x:c r="G16" t="str">
+      <x:c r="G20" s="3" t="str">
         <x:v>channels[0..]</x:v>
       </x:c>
-      <x:c r="H16" t="str">
+      <x:c r="H20" s="3" t="str">
         <x:v>mavros</x:v>
       </x:c>
-      <x:c r="I16" t="str">
+      <x:c r="I20" s="3" t="str">
         <x:v>multipoint / px4ctrl</x:v>
       </x:c>
-      <x:c r="J16" t="str">
+      <x:c r="J20" s="3" t="str">
         <x:v>mavros 已启动且 RC 在线</x:v>
       </x:c>
-      <x:c r="K16" t="str">
+      <x:c r="K20" s="3" t="str">
         <x:v>查看遥控器输入</x:v>
       </x:c>
-      <x:c r="L16" t="str">
+      <x:c r="L20" s="3" t="str">
         <x:v>rostopic echo -n 1 /mavros/rc/in</x:v>
       </x:c>
-      <x:c r="M16" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N16" t="str">
+      <x:c r="M20" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N20" s="3" t="str">
         <x:v>是安全门也是动作触发来源</x:v>
       </x:c>
-      <x:c r="O16" t="str">
+      <x:c r="O20" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P16" t="str">
+      <x:c r="P20" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
+    <x:row r="21">
+      <x:c r="A21" s="13" t="str">
         <x:v>I016</x:v>
       </x:c>
-      <x:c r="B17" t="str">
+      <x:c r="B21" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C17" t="str">
+      <x:c r="C21" s="3" t="str">
         <x:v>/mavros/imu/data</x:v>
       </x:c>
-      <x:c r="D17" t="str">
+      <x:c r="D21" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E17" t="str">
+      <x:c r="E21" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F17" t="str">
+      <x:c r="F21" s="3" t="str">
         <x:v>sensor_msgs/Imu</x:v>
       </x:c>
-      <x:c r="G17" t="str">
+      <x:c r="G21" s="3" t="str">
         <x:v>orientation angular_velocity linear_acceleration</x:v>
       </x:c>
-      <x:c r="H17" t="str">
+      <x:c r="H21" s="3" t="str">
         <x:v>mavros</x:v>
       </x:c>
-      <x:c r="I17" t="str">
+      <x:c r="I21" s="3" t="str">
         <x:v>px4ctrl</x:v>
       </x:c>
-      <x:c r="J17" t="str">
+      <x:c r="J21" s="3" t="str">
         <x:v>mavros 已启动</x:v>
       </x:c>
-      <x:c r="K17" t="str">
+      <x:c r="K21" s="3" t="str">
         <x:v>飞控 IMU 输入</x:v>
       </x:c>
-      <x:c r="L17" t="str">
+      <x:c r="L21" s="3" t="str">
         <x:v>rostopic echo -n 1 /mavros/imu/data</x:v>
       </x:c>
-      <x:c r="M17" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N17" t="str">
+      <x:c r="M21" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N21" s="3" t="str">
         <x:v>px4ctrl 明确使用 data 非 data_raw</x:v>
       </x:c>
-      <x:c r="O17" t="str">
+      <x:c r="O21" s="3" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
-      <x:c r="P17" t="str">
+      <x:c r="P21" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/realflight_modules/px4ctrl/src/px4ctrl_node.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="str">
+    <x:row r="22">
+      <x:c r="A22" s="13" t="str">
         <x:v>I017</x:v>
       </x:c>
-      <x:c r="B18" t="str">
+      <x:c r="B22" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C18" t="str">
+      <x:c r="C22" s="3" t="str">
         <x:v>/mavros/local_position/pose</x:v>
       </x:c>
-      <x:c r="D18" t="str">
+      <x:c r="D22" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E18" t="str">
+      <x:c r="E22" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F18" t="str">
+      <x:c r="F22" s="3" t="str">
         <x:v>geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G18" t="str">
+      <x:c r="G22" s="3" t="str">
         <x:v>pose</x:v>
       </x:c>
-      <x:c r="H18" t="str">
+      <x:c r="H22" s="3" t="str">
         <x:v>mavros</x:v>
       </x:c>
-      <x:c r="I18" t="str">
+      <x:c r="I22" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="J18" t="str">
+      <x:c r="J22" s="3" t="str">
         <x:v>mavros 已启动</x:v>
       </x:c>
-      <x:c r="K18" t="str">
+      <x:c r="K22" s="3" t="str">
         <x:v>查看 PX4 本地位姿</x:v>
       </x:c>
-      <x:c r="L18" t="str">
+      <x:c r="L22" s="3" t="str">
         <x:v>rostopic echo -n 1 /mavros/local_position/pose</x:v>
       </x:c>
-      <x:c r="M18" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N18" t="str">
+      <x:c r="M22" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N22" s="3" t="str">
         <x:v>与机载 EKF 输出不同源</x:v>
       </x:c>
-      <x:c r="O18" t="str">
+      <x:c r="O22" s="3" t="str">
         <x:v>E013_battery_topic</x:v>
       </x:c>
-      <x:c r="P18" t="str">
+      <x:c r="P22" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
+    <x:row r="23">
+      <x:c r="A23" s="13" t="str">
         <x:v>I018</x:v>
       </x:c>
-      <x:c r="B19" t="str">
+      <x:c r="B23" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C19" t="str">
+      <x:c r="C23" s="3" t="str">
         <x:v>/ekf/ekf_odom</x:v>
       </x:c>
-      <x:c r="D19" t="str">
+      <x:c r="D23" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E19" t="str">
+      <x:c r="E23" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F19" t="str">
+      <x:c r="F23" s="3" t="str">
         <x:v>nav_msgs/Odometry</x:v>
       </x:c>
-      <x:c r="G19" t="str">
+      <x:c r="G23" s="3" t="str">
         <x:v>pose twist</x:v>
       </x:c>
-      <x:c r="H19" t="str">
+      <x:c r="H23" s="3" t="str">
         <x:v>ekf</x:v>
       </x:c>
-      <x:c r="I19" t="str">
+      <x:c r="I23" s="3" t="str">
         <x:v>planner / operator</x:v>
       </x:c>
-      <x:c r="J19" t="str">
+      <x:c r="J23" s="3" t="str">
         <x:v>LIO 主链已启动</x:v>
       </x:c>
-      <x:c r="K19" t="str">
+      <x:c r="K23" s="3" t="str">
         <x:v>查看融合 odom</x:v>
       </x:c>
-      <x:c r="L19" t="str">
+      <x:c r="L23" s="3" t="str">
         <x:v>rostopic echo -n 1 /ekf/ekf_odom</x:v>
       </x:c>
-      <x:c r="M19" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N19" t="str">
+      <x:c r="M23" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N23" s="3" t="str">
         <x:v>LIO 主链下的核心定位输出</x:v>
       </x:c>
-      <x:c r="O19" t="str">
+      <x:c r="O23" s="3" t="str">
         <x:v>E012_ekf_output</x:v>
       </x:c>
-      <x:c r="P19" t="str">
+      <x:c r="P23" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="str">
+    <x:row r="24">
+      <x:c r="A24" s="13" t="str">
         <x:v>I019</x:v>
       </x:c>
-      <x:c r="B20" t="str">
+      <x:c r="B24" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C20" t="str">
+      <x:c r="C24" s="3" t="str">
         <x:v>/laserMapping/odometry</x:v>
       </x:c>
-      <x:c r="D20" t="str">
+      <x:c r="D24" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E20" t="str">
+      <x:c r="E24" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F20" t="str">
+      <x:c r="F24" s="3" t="str">
         <x:v>nav_msgs/Odometry</x:v>
       </x:c>
-      <x:c r="G20" t="str">
+      <x:c r="G24" s="3" t="str">
         <x:v>pose twist</x:v>
       </x:c>
-      <x:c r="H20" t="str">
+      <x:c r="H24" s="3" t="str">
         <x:v>faster_lio</x:v>
       </x:c>
-      <x:c r="I20" t="str">
+      <x:c r="I24" s="3" t="str">
         <x:v>ekf / operator</x:v>
       </x:c>
-      <x:c r="J20" t="str">
+      <x:c r="J24" s="3" t="str">
         <x:v>faster_lio 已启动</x:v>
       </x:c>
-      <x:c r="K20" t="str">
+      <x:c r="K24" s="3" t="str">
         <x:v>查看雷达 odom</x:v>
       </x:c>
-      <x:c r="L20" t="str">
+      <x:c r="L24" s="3" t="str">
         <x:v>rostopic echo -n 1 /laserMapping/odometry</x:v>
       </x:c>
-      <x:c r="M20" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N20" t="str">
+      <x:c r="M24" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N24" s="3" t="str">
         <x:v>ekf 会依赖它</x:v>
       </x:c>
-      <x:c r="O20" t="str">
+      <x:c r="O24" s="3" t="str">
         <x:v>E012_ekf_output</x:v>
       </x:c>
-      <x:c r="P20" t="str">
+      <x:c r="P24" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="str">
+    <x:row r="25">
+      <x:c r="A25" s="13" t="str">
         <x:v>I020</x:v>
       </x:c>
-      <x:c r="B21" t="str">
+      <x:c r="B25" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C21" t="str">
+      <x:c r="C25" s="3" t="str">
         <x:v>/laserMapping/cloud_registered</x:v>
       </x:c>
-      <x:c r="D21" t="str">
+      <x:c r="D25" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E21" t="str">
+      <x:c r="E25" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F21" t="str">
+      <x:c r="F25" s="3" t="str">
         <x:v>sensor_msgs/PointCloud2</x:v>
       </x:c>
-      <x:c r="G21" t="str">
+      <x:c r="G25" s="3" t="str">
         <x:v>point cloud</x:v>
       </x:c>
-      <x:c r="H21" t="str">
+      <x:c r="H25" s="3" t="str">
         <x:v>faster_lio</x:v>
       </x:c>
-      <x:c r="I21" t="str">
+      <x:c r="I25" s="3" t="str">
         <x:v>planner / rviz</x:v>
       </x:c>
-      <x:c r="J21" t="str">
+      <x:c r="J25" s="3" t="str">
         <x:v>faster_lio 已启动</x:v>
       </x:c>
-      <x:c r="K21" t="str">
+      <x:c r="K25" s="3" t="str">
         <x:v>查看规划输入点云</x:v>
       </x:c>
-      <x:c r="L21" t="str">
+      <x:c r="L25" s="3" t="str">
         <x:v>rostopic hz /laserMapping/cloud_registered</x:v>
       </x:c>
-      <x:c r="M21" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N21" t="str">
+      <x:c r="M25" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N25" s="3" t="str">
         <x:v>rviz 观察质量时重点看它</x:v>
       </x:c>
-      <x:c r="O21" t="str">
+      <x:c r="O25" s="3" t="str">
         <x:v>E012_ekf_output</x:v>
       </x:c>
-      <x:c r="P21" t="str">
+      <x:c r="P25" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
+    <x:row r="26">
+      <x:c r="A26" s="13" t="str">
         <x:v>I021</x:v>
       </x:c>
-      <x:c r="B22" t="str">
+      <x:c r="B26" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C22" t="str">
+      <x:c r="C26" s="3" t="str">
         <x:v>/vins/imu_propagate</x:v>
       </x:c>
-      <x:c r="D22" t="str">
+      <x:c r="D26" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E22" t="str">
+      <x:c r="E26" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F22" t="str">
+      <x:c r="F26" s="3" t="str">
         <x:v>nav_msgs/Odometry</x:v>
       </x:c>
-      <x:c r="G22" t="str">
+      <x:c r="G26" s="3" t="str">
         <x:v>pose twist</x:v>
       </x:c>
-      <x:c r="H22" t="str">
+      <x:c r="H26" s="3" t="str">
         <x:v>vins</x:v>
       </x:c>
-      <x:c r="I22" t="str">
+      <x:c r="I26" s="3" t="str">
         <x:v>planner / operator</x:v>
       </x:c>
-      <x:c r="J22" t="str">
+      <x:c r="J26" s="3" t="str">
         <x:v>VIO 主链已启动</x:v>
       </x:c>
-      <x:c r="K22" t="str">
+      <x:c r="K26" s="3" t="str">
         <x:v>查看视觉惯性 odom</x:v>
       </x:c>
-      <x:c r="L22" t="str">
+      <x:c r="L26" s="3" t="str">
         <x:v>rostopic echo -n 1 /vins/imu_propagate</x:v>
       </x:c>
-      <x:c r="M22" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N22" t="str">
+      <x:c r="M26" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N26" s="3" t="str">
         <x:v>当前视觉定位主输出</x:v>
       </x:c>
-      <x:c r="O22" t="str">
+      <x:c r="O26" s="3" t="str">
         <x:v>E011_vins_output</x:v>
       </x:c>
-      <x:c r="P22" t="str">
+      <x:c r="P26" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="str">
+    <x:row r="27">
+      <x:c r="A27" s="13" t="str">
         <x:v>I022</x:v>
       </x:c>
-      <x:c r="B23" t="str">
+      <x:c r="B27" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C23" t="str">
+      <x:c r="C27" s="3" t="str">
         <x:v>/drone_0_planning/trajectory</x:v>
       </x:c>
-      <x:c r="D23" t="str">
+      <x:c r="D27" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E23" t="str">
+      <x:c r="E27" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F23" t="str">
+      <x:c r="F27" s="3" t="str">
         <x:v>traj_utils/PolyTraj</x:v>
       </x:c>
-      <x:c r="G23" t="str">
+      <x:c r="G27" s="3" t="str">
         <x:v>trajectory</x:v>
       </x:c>
-      <x:c r="H23" t="str">
+      <x:c r="H27" s="3" t="str">
         <x:v>traj_server</x:v>
       </x:c>
-      <x:c r="I23" t="str">
+      <x:c r="I27" s="3" t="str">
         <x:v>operator / px4ctrl</x:v>
       </x:c>
-      <x:c r="J23" t="str">
+      <x:c r="J27" s="3" t="str">
         <x:v>规划链已启动</x:v>
       </x:c>
-      <x:c r="K23" t="str">
+      <x:c r="K27" s="3" t="str">
         <x:v>查看当前规划结果</x:v>
       </x:c>
-      <x:c r="L23" t="str">
+      <x:c r="L27" s="3" t="str">
         <x:v>rostopic echo -n 1 /drone_0_planning/trajectory</x:v>
       </x:c>
-      <x:c r="M23" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N23" t="str">
+      <x:c r="M27" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N27" s="3" t="str">
         <x:v>轨迹有了不等于控制器一定执行</x:v>
       </x:c>
-      <x:c r="O23" t="str">
+      <x:c r="O27" s="3" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
-      <x:c r="P23" t="str">
+      <x:c r="P27" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/diff_planner/plan_manage/launch/exp/run_exp_single_lio.launch</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="str">
+    <x:row r="28">
+      <x:c r="A28" s="13" t="str">
         <x:v>I023</x:v>
       </x:c>
-      <x:c r="B24" t="str">
+      <x:c r="B28" s="3" t="str">
         <x:v>parameter</x:v>
       </x:c>
-      <x:c r="C24" t="str">
+      <x:c r="C28" s="3" t="str">
         <x:v>points.yaml</x:v>
       </x:c>
-      <x:c r="D24" t="str">
+      <x:c r="D28" s="3" t="str">
         <x:v>file</x:v>
       </x:c>
-      <x:c r="E24" t="str">
+      <x:c r="E28" s="3" t="str">
         <x:v>read</x:v>
       </x:c>
-      <x:c r="F24" t="str">
+      <x:c r="F28" s="3" t="str">
         <x:v>yaml</x:v>
       </x:c>
-      <x:c r="G24" t="str">
+      <x:c r="G28" s="3" t="str">
         <x:v>test1 test2 test3 test4 test_back</x:v>
       </x:c>
-      <x:c r="H24" t="str">
+      <x:c r="H28" s="3" t="str">
         <x:v>multipoint config</x:v>
       </x:c>
-      <x:c r="I24" t="str">
+      <x:c r="I28" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="J24" t="str">
+      <x:c r="J28" s="3" t="str">
         <x:v>任务模式与航点格式要匹配</x:v>
       </x:c>
-      <x:c r="K24" t="str">
+      <x:c r="K28" s="3" t="str">
         <x:v>定义任务点和返程点</x:v>
       </x:c>
-      <x:c r="L24" t="str">
+      <x:c r="L28" s="3" t="str">
         <x:v>src/user_command/multipoint/config/points.yaml</x:v>
       </x:c>
-      <x:c r="M24" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N24" t="str">
+      <x:c r="M28" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N28" s="3" t="str">
         <x:v>数组长度错会直接读取失败</x:v>
       </x:c>
-      <x:c r="O24" t="str">
+      <x:c r="O28" s="3" t="str">
         <x:v>E015_points_yaml</x:v>
       </x:c>
-      <x:c r="P24" t="str">
+      <x:c r="P28" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/config/points.yaml</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
+    <x:row r="29">
+      <x:c r="A29" s="13" t="str">
         <x:v>I024</x:v>
       </x:c>
-      <x:c r="B25" t="str">
+      <x:c r="B29" s="3" t="str">
         <x:v>parameter</x:v>
       </x:c>
-      <x:c r="C25" t="str">
+      <x:c r="C29" s="3" t="str">
         <x:v>ctrl_param_fpv.yaml</x:v>
       </x:c>
-      <x:c r="D25" t="str">
+      <x:c r="D29" s="3" t="str">
         <x:v>file</x:v>
       </x:c>
-      <x:c r="E25" t="str">
+      <x:c r="E29" s="3" t="str">
         <x:v>read</x:v>
       </x:c>
-      <x:c r="F25" t="str">
+      <x:c r="F29" s="3" t="str">
         <x:v>yaml</x:v>
       </x:c>
-      <x:c r="G25" t="str">
+      <x:c r="G29" s="3" t="str">
         <x:v>low_voltage takeoff_height takeoff_land_speed</x:v>
       </x:c>
-      <x:c r="H25" t="str">
+      <x:c r="H29" s="3" t="str">
         <x:v>px4ctrl config</x:v>
       </x:c>
-      <x:c r="I25" t="str">
+      <x:c r="I29" s="3" t="str">
         <x:v>px4ctrl</x:v>
       </x:c>
-      <x:c r="J25" t="str">
+      <x:c r="J29" s="3" t="str">
         <x:v>px4ctrl 启动前读取</x:v>
       </x:c>
-      <x:c r="K25" t="str">
+      <x:c r="K29" s="3" t="str">
         <x:v>控制起飞高度和电池阈值</x:v>
       </x:c>
-      <x:c r="L25" t="str">
+      <x:c r="L29" s="3" t="str">
         <x:v>src/realflight_modules/px4ctrl/config/ctrl_param_fpv.yaml</x:v>
       </x:c>
-      <x:c r="M25" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N25" t="str">
+      <x:c r="M29" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N29" s="3" t="str">
         <x:v>改前必须确认起飞高度范围无障碍</x:v>
       </x:c>
-      <x:c r="O25" t="str">
+      <x:c r="O29" s="3" t="str">
         <x:v>E014_ctrl_params</x:v>
       </x:c>
-      <x:c r="P25" t="str">
+      <x:c r="P29" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/realflight_modules/px4ctrl/config/ctrl_param_fpv.yaml</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
+    <x:row r="30">
+      <x:c r="A30" s="13" t="str">
         <x:v>I025</x:v>
       </x:c>
-      <x:c r="B26" t="str">
+      <x:c r="B30" s="3" t="str">
         <x:v>parameter</x:v>
       </x:c>
-      <x:c r="C26" t="str">
+      <x:c r="C30" s="3" t="str">
         <x:v>multipointplan_exp_lio.launch</x:v>
       </x:c>
-      <x:c r="D26" t="str">
+      <x:c r="D30" s="3" t="str">
         <x:v>file</x:v>
       </x:c>
-      <x:c r="E26" t="str">
+      <x:c r="E30" s="3" t="str">
         <x:v>read</x:v>
       </x:c>
-      <x:c r="F26" t="str">
+      <x:c r="F30" s="3" t="str">
         <x:v>roslaunch args</x:v>
       </x:c>
-      <x:c r="G26" t="str">
+      <x:c r="G30" s="3" t="str">
         <x:v>fligt_type next_distance start_plan back_plan</x:v>
       </x:c>
-      <x:c r="H26" t="str">
+      <x:c r="H30" s="3" t="str">
         <x:v>launch config</x:v>
       </x:c>
-      <x:c r="I26" t="str">
+      <x:c r="I30" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="J26" t="str">
+      <x:c r="J30" s="3" t="str">
         <x:v>LIO 任务链启动前读取</x:v>
       </x:c>
-      <x:c r="K26" t="str">
+      <x:c r="K30" s="3" t="str">
         <x:v>选择航点模式和触发行为</x:v>
       </x:c>
-      <x:c r="L26" t="str">
+      <x:c r="L30" s="3" t="str">
         <x:v>roslaunch multipoint multipointplan_exp_lio.launch</x:v>
       </x:c>
-      <x:c r="M26" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N26" t="str">
+      <x:c r="M30" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N30" s="3" t="str">
         <x:v>fligt_type 拼写就是源码现状 不要擅自改名</x:v>
       </x:c>
-      <x:c r="O26" t="str">
+      <x:c r="O30" s="3" t="str">
         <x:v>E015_points_yaml</x:v>
       </x:c>
-      <x:c r="P26" t="str">
+      <x:c r="P30" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/launch/multipointplan_exp_lio.launch</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
+    <x:row r="31">
+      <x:c r="A31" s="13" t="str">
         <x:v>I026</x:v>
       </x:c>
-      <x:c r="B27" t="str">
+      <x:c r="B31" s="3" t="str">
         <x:v>parameter</x:v>
       </x:c>
-      <x:c r="C27" t="str">
+      <x:c r="C31" s="3" t="str">
         <x:v>run_exp_single_lio.launch</x:v>
       </x:c>
-      <x:c r="D27" t="str">
+      <x:c r="D31" s="3" t="str">
         <x:v>file</x:v>
       </x:c>
-      <x:c r="E27" t="str">
+      <x:c r="E31" s="3" t="str">
         <x:v>read</x:v>
       </x:c>
-      <x:c r="F27" t="str">
+      <x:c r="F31" s="3" t="str">
         <x:v>roslaunch args</x:v>
       </x:c>
-      <x:c r="G27" t="str">
+      <x:c r="G31" s="3" t="str">
         <x:v>max_vel max_acc map_resolution flight_type</x:v>
       </x:c>
-      <x:c r="H27" t="str">
+      <x:c r="H31" s="3" t="str">
         <x:v>launch config</x:v>
       </x:c>
-      <x:c r="I27" t="str">
+      <x:c r="I31" s="3" t="str">
         <x:v>planner</x:v>
       </x:c>
-      <x:c r="J27" t="str">
+      <x:c r="J31" s="3" t="str">
         <x:v>LIO 规划链启动前读取</x:v>
       </x:c>
-      <x:c r="K27" t="str">
+      <x:c r="K31" s="3" t="str">
         <x:v>配置 LIO 规划参数</x:v>
       </x:c>
-      <x:c r="L27" t="str">
+      <x:c r="L31" s="3" t="str">
         <x:v>roslaunch diff_planner run_exp_single_lio.launch</x:v>
       </x:c>
-      <x:c r="M27" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N27" t="str">
+      <x:c r="M31" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N31" s="3" t="str">
         <x:v>是规划参数不是飞控参数</x:v>
       </x:c>
-      <x:c r="O27" t="str">
+      <x:c r="O31" s="3" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
-      <x:c r="P27" t="str">
+      <x:c r="P31" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/diff_planner/plan_manage/launch/exp/run_exp_single_lio.launch</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
-      <x:c r="A28" t="str">
+    <x:row r="32">
+      <x:c r="A32" s="13" t="str">
         <x:v>I027</x:v>
       </x:c>
-      <x:c r="B28" t="str">
+      <x:c r="B32" s="3" t="str">
         <x:v>parameter</x:v>
       </x:c>
-      <x:c r="C28" t="str">
+      <x:c r="C32" s="3" t="str">
         <x:v>run_exp_single_vio.launch</x:v>
       </x:c>
-      <x:c r="D28" t="str">
+      <x:c r="D32" s="3" t="str">
         <x:v>file</x:v>
       </x:c>
-      <x:c r="E28" t="str">
+      <x:c r="E32" s="3" t="str">
         <x:v>read</x:v>
       </x:c>
-      <x:c r="F28" t="str">
+      <x:c r="F32" s="3" t="str">
         <x:v>roslaunch args</x:v>
       </x:c>
-      <x:c r="G28" t="str">
+      <x:c r="G32" s="3" t="str">
         <x:v>cx cy fx fy max_vel max_acc</x:v>
       </x:c>
-      <x:c r="H28" t="str">
+      <x:c r="H32" s="3" t="str">
         <x:v>launch config</x:v>
       </x:c>
-      <x:c r="I28" t="str">
+      <x:c r="I32" s="3" t="str">
         <x:v>planner</x:v>
       </x:c>
-      <x:c r="J28" t="str">
+      <x:c r="J32" s="3" t="str">
         <x:v>VIO 规划链启动前读取</x:v>
       </x:c>
-      <x:c r="K28" t="str">
+      <x:c r="K32" s="3" t="str">
         <x:v>配置 VIO 规划参数</x:v>
       </x:c>
-      <x:c r="L28" t="str">
+      <x:c r="L32" s="3" t="str">
         <x:v>roslaunch diff_planner run_exp_single_vio.launch</x:v>
       </x:c>
-      <x:c r="M28" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N28" t="str">
+      <x:c r="M32" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N32" s="3" t="str">
         <x:v>视觉内参错误会直接破坏 VIO 规划</x:v>
       </x:c>
-      <x:c r="O28" t="str">
+      <x:c r="O32" s="3" t="str">
         <x:v>E007_run_single_vio_script</x:v>
       </x:c>
-      <x:c r="P28" t="str">
+      <x:c r="P32" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/diff_planner/plan_manage/launch/exp/run_exp_single_vio.launch</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
-      <x:c r="A29" t="str">
+    <x:row r="33">
+      <x:c r="A33" s="13" t="str">
         <x:v>I028</x:v>
       </x:c>
-      <x:c r="B29" t="str">
+      <x:c r="B33" s="3" t="str">
         <x:v>rc</x:v>
       </x:c>
-      <x:c r="C29" t="str">
+      <x:c r="C33" s="3" t="str">
         <x:v>RC Channel 5</x:v>
       </x:c>
-      <x:c r="D29" t="str">
+      <x:c r="D33" s="3" t="str">
         <x:v>physical_input</x:v>
       </x:c>
-      <x:c r="E29" t="str">
+      <x:c r="E33" s="3" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F29" t="str">
+      <x:c r="F33" s="3" t="str">
         <x:v>remote control</x:v>
       </x:c>
-      <x:c r="G29" t="str">
+      <x:c r="G33" s="3" t="str">
         <x:v>光流 / 姿态 / onboard</x:v>
       </x:c>
-      <x:c r="H29" t="str">
+      <x:c r="H33" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I29" t="str">
+      <x:c r="I33" s="3" t="str">
         <x:v>PX4 / px4ctrl</x:v>
       </x:c>
-      <x:c r="J29" t="str">
+      <x:c r="J33" s="3" t="str">
         <x:v>遥控器在线</x:v>
       </x:c>
-      <x:c r="K29" t="str">
+      <x:c r="K33" s="3" t="str">
         <x:v>切换飞行模式</x:v>
       </x:c>
-      <x:c r="L29" t="str">
+      <x:c r="L33" s="3" t="str">
         <x:v>上=光流 中=姿态 下=onboard</x:v>
       </x:c>
-      <x:c r="M29" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N29" t="str">
+      <x:c r="M33" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N33" s="3" t="str">
         <x:v>软件控制会被它打断</x:v>
       </x:c>
-      <x:c r="O29" t="str">
+      <x:c r="O33" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P29" t="str">
+      <x:c r="P33" s="14" t="str">
         <x:v>uav/10-knowledge-base/01-硬件与系统.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
-      <x:c r="A30" t="str">
+    <x:row r="34">
+      <x:c r="A34" s="13" t="str">
         <x:v>I029</x:v>
       </x:c>
-      <x:c r="B30" t="str">
+      <x:c r="B34" s="3" t="str">
         <x:v>rc</x:v>
       </x:c>
-      <x:c r="C30" t="str">
+      <x:c r="C34" s="3" t="str">
         <x:v>RC Channel 6</x:v>
       </x:c>
-      <x:c r="D30" t="str">
+      <x:c r="D34" s="3" t="str">
         <x:v>physical_input</x:v>
       </x:c>
-      <x:c r="E30" t="str">
+      <x:c r="E34" s="3" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F30" t="str">
+      <x:c r="F34" s="3" t="str">
         <x:v>remote control</x:v>
       </x:c>
-      <x:c r="G30" t="str">
+      <x:c r="G34" s="3" t="str">
         <x:v>悬停 / 轨迹</x:v>
       </x:c>
-      <x:c r="H30" t="str">
+      <x:c r="H34" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I30" t="str">
+      <x:c r="I34" s="3" t="str">
         <x:v>PX4 / px4ctrl</x:v>
       </x:c>
-      <x:c r="J30" t="str">
+      <x:c r="J34" s="3" t="str">
         <x:v>遥控器在线</x:v>
       </x:c>
-      <x:c r="K30" t="str">
+      <x:c r="K34" s="3" t="str">
         <x:v>切换悬停与轨迹控制</x:v>
       </x:c>
-      <x:c r="L30" t="str">
+      <x:c r="L34" s="3" t="str">
         <x:v>上=悬停 下=轨迹</x:v>
       </x:c>
-      <x:c r="M30" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N30" t="str">
+      <x:c r="M34" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N34" s="3" t="str">
         <x:v>异常时上拨 6 通是重要兜底</x:v>
       </x:c>
-      <x:c r="O30" t="str">
+      <x:c r="O34" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P30" t="str">
+      <x:c r="P34" s="14" t="str">
         <x:v>uav/10-knowledge-base/01-硬件与系统.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
-      <x:c r="A31" t="str">
+    <x:row r="35">
+      <x:c r="A35" s="13" t="str">
         <x:v>I030</x:v>
       </x:c>
-      <x:c r="B31" t="str">
+      <x:c r="B35" s="3" t="str">
         <x:v>rc</x:v>
       </x:c>
-      <x:c r="C31" t="str">
+      <x:c r="C35" s="3" t="str">
         <x:v>RC Channel 7</x:v>
       </x:c>
-      <x:c r="D31" t="str">
+      <x:c r="D35" s="3" t="str">
         <x:v>physical_input</x:v>
       </x:c>
-      <x:c r="E31" t="str">
+      <x:c r="E35" s="3" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F31" t="str">
+      <x:c r="F35" s="3" t="str">
         <x:v>remote control</x:v>
       </x:c>
-      <x:c r="G31" t="str">
+      <x:c r="G35" s="3" t="str">
         <x:v>解锁 / 锁桨 / 急停</x:v>
       </x:c>
-      <x:c r="H31" t="str">
+      <x:c r="H35" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I31" t="str">
+      <x:c r="I35" s="3" t="str">
         <x:v>PX4</x:v>
       </x:c>
-      <x:c r="J31" t="str">
+      <x:c r="J35" s="3" t="str">
         <x:v>遥控器在线</x:v>
       </x:c>
-      <x:c r="K31" t="str">
+      <x:c r="K35" s="3" t="str">
         <x:v>电机安全控制</x:v>
       </x:c>
-      <x:c r="L31" t="str">
+      <x:c r="L35" s="3" t="str">
         <x:v>上=解锁 下=急停</x:v>
       </x:c>
-      <x:c r="M31" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N31" t="str">
+      <x:c r="M35" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N35" s="3" t="str">
         <x:v>最高安全优先级</x:v>
       </x:c>
-      <x:c r="O31" t="str">
+      <x:c r="O35" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P31" t="str">
+      <x:c r="P35" s="14" t="str">
         <x:v>uav/10-knowledge-base/01-硬件与系统.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
-      <x:c r="A32" t="str">
+    <x:row r="36">
+      <x:c r="A36" s="15" t="str">
         <x:v>I031</x:v>
       </x:c>
-      <x:c r="B32" t="str">
+      <x:c r="B36" s="16" t="str">
         <x:v>rc</x:v>
       </x:c>
-      <x:c r="C32" t="str">
+      <x:c r="C36" s="16" t="str">
         <x:v>RC Channel 8</x:v>
       </x:c>
-      <x:c r="D32" t="str">
+      <x:c r="D36" s="16" t="str">
         <x:v>physical_input</x:v>
       </x:c>
-      <x:c r="E32" t="str">
+      <x:c r="E36" s="16" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F32" t="str">
+      <x:c r="F36" s="16" t="str">
         <x:v>remote control</x:v>
       </x:c>
-      <x:c r="G32" t="str">
+      <x:c r="G36" s="16" t="str">
         <x:v>下-&gt;中 takeoff 中-&gt;上 start 上-&gt;中 back 中-&gt;下 land</x:v>
       </x:c>
-      <x:c r="H32" t="str">
+      <x:c r="H36" s="16" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I32" t="str">
+      <x:c r="I36" s="16" t="str">
         <x:v>multipoint / PX4</x:v>
       </x:c>
-      <x:c r="J32" t="str">
+      <x:c r="J36" s="16" t="str">
         <x:v>遥控器在线且 mavros/rc/in 正常</x:v>
       </x:c>
-      <x:c r="K32" t="str">
+      <x:c r="K36" s="16" t="str">
         <x:v>任务动作触发</x:v>
       </x:c>
-      <x:c r="L32" t="str">
+      <x:c r="L36" s="16" t="str">
         <x:v>下/中/上 档位切换</x:v>
       </x:c>
-      <x:c r="M32" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N32" t="str">
+      <x:c r="M36" s="16" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N36" s="16" t="str">
         <x:v>脚本与 RC 触发方式不要混用</x:v>
       </x:c>
-      <x:c r="O32" t="str">
+      <x:c r="O36" s="16" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P32" t="str">
+      <x:c r="P36" s="17" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>

--- a/docs/非凸α-接口总表.xlsx
+++ b/docs/非凸α-接口总表.xlsx
@@ -2,7 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口总表" sheetId="1" r:id="Rc1aa8081fad1487a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="怎么用" sheetId="1" r:id="Radf1307a5740490e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推荐接入" sheetId="2" r:id="Ra141166dbfc94915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景速查" sheetId="3" r:id="R3ee6260a42214969"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态接口" sheetId="4" r:id="R69b5f882f29b40f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动作接口" sheetId="5" r:id="Rf9364226b65f445d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="脚本入口" sheetId="6" r:id="R60ab7a58e7e44d14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数入口" sheetId="7" r:id="R101be8713c9d4dc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RC映射" sheetId="8" r:id="R656282a134004641"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整原表" sheetId="9" r:id="R38aa0403c3d648b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,28 +21,156 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color theme="0"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="444444"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="0"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4" tint="0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="5" tint="0.35"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="9">
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="D9D9D9"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -190,1604 +326,3437 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="25.149999618530273" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="43.560001373291016" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="str">
+      <x:c r="A1" s="2" t="str">
+        <x:v>非凸α接口总表怎么用</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这份表不是让你逐行背。先看“推荐接入”，再按任务去看状态接口、动作接口、脚本入口、参数入口和 RC 映射，最后才看完整原表。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>先按你的问题去找 sheet</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>我现在要做什么</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>先看哪个 sheet</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>为什么</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>不想按类别读，想按任务场景直接找</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>场景速查</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>把日常最常见的开发和排查场景压成一张表，先看这里最快。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>判断上层系统先接哪些接口</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>推荐接入</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>这里把当前机器最值得先订阅和先发布的接口浓缩好了。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>看电量、状态、定位</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>状态接口</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>这是日常观测入口，先订阅这些再谈上层逻辑。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>触发起飞、开始任务、返程、降落</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>动作接口</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>这些是当前机器已经稳定落地的动作原语。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>搞清楚一键脚本到底起了什么</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>脚本入口</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>这里把 run_single_lio/vio 和动作脚本拆开写了。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>想改航点、起飞高度、规划参数</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>参数入口</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>这里告诉你该改哪个文件，不用翻整仓。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>想确认遥控器会不会打断软件</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>RC映射</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>RC 是最高优先级安全边界，这里单独列出。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="15" t="str">
+        <x:v>要追溯到原始事实</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="str">
+        <x:v>完整原表</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:v>保留全部字段，便于追源码和证据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="6" t="str">
+        <x:v>给上层系统的最小闭环</x:v>
+      </x:c>
+      <x:c r="B16" s="6"/>
+      <x:c r="C16" s="6"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="9" t="str">
+        <x:v>目标</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="str">
+        <x:v>推荐接口</x:v>
+      </x:c>
+      <x:c r="C17" s="9" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
+        <x:v>状态订阅</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="str">
+        <x:v>/mavros/state, /mavros/battery, /mavros/rc/in</x:v>
+      </x:c>
+      <x:c r="C18" s="12" t="str">
+        <x:v>先拿到飞控、供电和 RC 安全门，别一上来就发控制。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="13" t="str">
+        <x:v>定位订阅</x:v>
+      </x:c>
+      <x:c r="B19" s="3" t="str">
+        <x:v>/ekf/ekf_odom 或 /vins/imu_propagate</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str">
+        <x:v>LIO/VIO 二选一，根据当前启动链决定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="13" t="str">
+        <x:v>动作发布</x:v>
+      </x:c>
+      <x:c r="B20" s="3" t="str">
+        <x:v>/px4ctrl/takeoff_land, /move_base_simple/goal, /back_trigger</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="str">
+        <x:v>这是当前机器最适合上层系统直接调用的动作层。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="15" t="str">
+        <x:v>先别碰</x:v>
+      </x:c>
+      <x:c r="B21" s="16" t="str">
+        <x:v>/setpoints_cmd 和 px4ctrl 内部状态机</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="str">
+        <x:v>这两层风险更高，不适合作为第一接入点。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="31.290000915527344" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>推荐接入</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>如果你要做二开，先围绕这 8 个接口建立闭环，不要第一步就下钻到控制器内部。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>建议你先围绕这些接口做开发</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>接入目标</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>接口</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>类型</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>方向</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>怎么用</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>前置条件</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="str">
+        <x:v>风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>看飞控连接与模式</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>/mavros/state</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>查看飞控连接与模式</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>mavros 已启动</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str">
+        <x:v>最先判断 FCU 是否连上</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>看电量</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>/mavros/battery</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>查看电量</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="str">
+        <x:v>mavros 已启动</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
+        <x:v>低压阈值与 ctrl_param_fpv.yaml 联动</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>看 RC 安全门</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>/mavros/rc/in</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>查看遥控器输入</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="str">
+        <x:v>mavros 已启动且 RC 在线</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>是安全门也是动作触发来源</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>看 LIO 定位</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>/ekf/ekf_odom</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>查看融合 odom</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="str">
+        <x:v>LIO 主链已启动</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>LIO 主链下的核心定位输出</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>看 VIO 定位</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>/vins/imu_propagate</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>查看视觉惯性 odom</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
+        <x:v>VIO 主链已启动</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>当前视觉定位主输出</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>触发起飞/降落</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>/px4ctrl/takeoff_land</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>起飞与降落动作原语</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
+        <x:v>px4ctrl 与定位链正常</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>RC 档位不对会被拒绝</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>触发开始任务</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>/move_base_simple/goal</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>开始执行点位任务</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
+        <x:v>multipoint 启动且 start_plan=1</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>不要和 RC 八通重复发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="15" t="str">
+        <x:v>触发返程</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="str">
+        <x:v>/back_trigger</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="str">
+        <x:v>ros_topic</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="str">
+        <x:v>开始返程任务</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="str">
+        <x:v>multipoint 启动且 back_plan=1</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="str">
+        <x:v>返回路径依赖 test_back</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="17.790000915527344" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28.829999923706055" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="31.290000915527344" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>场景速查</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>如果你已经知道自己要做什么，就先从这一页进，不要先扎进完整原表。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>按场景找入口</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>先做什么</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>关键接口/文件</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>深挖去哪</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>看电量</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>先确认 mavros 在线</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>/mavros/battery</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>状态接口</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="str">
+        <x:v>最常用日常检查项，先看电压和 percentage。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>看飞控状态</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>先看连接、armed、mode</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>/mavros/state</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>状态接口</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>起飞前和排障时都应先看它。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>看定位是否正常</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>按当前启动链选 LIO 或 VIO</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>/ekf/ekf_odom 或 /vins/imu_propagate</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>状态接口</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>LIO/VIO 二选一，不要混着判断。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>看 RC 会不会打断软件</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>先看原始通道，再看通道含义</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>/mavros/rc/in + RC Channel 5/6/7/8</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>RC映射</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>RC 是最高优先级安全边界。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>触发起飞</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>确认前置条件后再发动作</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>/px4ctrl/takeoff_land 或 takeoff.sh</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>动作接口 / 脚本入口</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>takeoff_land_cmd=1；RC 档位不对时会被拒绝。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>开始任务</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>触发任务入口，不直接发底层控制</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>/move_base_simple/goal 或 pub_trigger.sh</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>动作接口 / 脚本入口</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>当前多点任务最自然的开始入口。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>返程</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>走返程 trigger，不要直接猜返回点逻辑</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>/back_trigger 或 back.sh</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>动作接口 / 脚本入口</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>具体返程点来自 points.yaml 里的 test_back。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>降落</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="str">
+        <x:v>优先用已有动作原语</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>/px4ctrl/takeoff_land 或 land.sh</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>动作接口 / 脚本入口</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>takeoff_land_cmd=2；与起飞共用同一 topic。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>改航点</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="str">
+        <x:v>先改 YAML，再确认模式</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>points.yaml + multipointplan_exp_lio.launch</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="str">
+        <x:v>参数入口</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>先确认 fligt_type，再按 test1~test4 格式改。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>改起飞高度</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="str">
+        <x:v>只改控制器参数，不要误改规划参数</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="str">
+        <x:v>ctrl_param_fpv.yaml</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="str">
+        <x:v>参数入口</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="str">
+        <x:v>对应 auto_takeoff_land.takeoff_height。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="15" t="str">
+        <x:v>接上层 Agent / MQTT</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
+        <x:v>先做状态订阅和动作发布闭环</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="str">
+        <x:v>/mavros/state, /mavros/battery, /px4ctrl/takeoff_land, /move_base_simple/goal</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="str">
+        <x:v>推荐接入</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="str">
+        <x:v>第一刀不要碰 /setpoints_cmd 和 px4ctrl 状态机。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.109999656677246" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>状态接口</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>日常观察先从这里开始。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+      <x:c r="H2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>当前最常用的状态类接口</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>接口</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>消息类型</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>上游</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>下游/使用者</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>用途</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>常用命令</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="str">
+        <x:v>风险/备注</x:v>
+      </x:c>
+      <x:c r="H5" s="9" t="str">
+        <x:v>当前状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>/mavros/state</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>mavros_msgs/State</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>mavros</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>operator / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>查看飞控连接与模式</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>rostopic echo -n 1 /mavros/state</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>最先判断 FCU 是否连上</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>/mavros/battery</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>sensor_msgs/BatteryState</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>mavros</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>operator / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>查看电量</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="str">
+        <x:v>rostopic echo -n 1 /mavros/battery</x:v>
+      </x:c>
+      <x:c r="G7" s="3" t="str">
+        <x:v>低压阈值与 ctrl_param_fpv.yaml 联动</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>/mavros/rc/in</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>mavros_msgs/RCIn</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>mavros</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>multipoint / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>查看遥控器输入</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="str">
+        <x:v>rostopic echo -n 1 /mavros/rc/in</x:v>
+      </x:c>
+      <x:c r="G8" s="3" t="str">
+        <x:v>是安全门也是动作触发来源</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>/mavros/imu/data</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>sensor_msgs/Imu</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>mavros</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>px4ctrl</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>飞控 IMU 输入</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="str">
+        <x:v>rostopic echo -n 1 /mavros/imu/data</x:v>
+      </x:c>
+      <x:c r="G9" s="3" t="str">
+        <x:v>px4ctrl 明确使用 data 非 data_raw</x:v>
+      </x:c>
+      <x:c r="H9" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>/mavros/local_position/pose</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>mavros</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>operator</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>查看 PX4 本地位姿</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
+        <x:v>rostopic echo -n 1 /mavros/local_position/pose</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="str">
+        <x:v>与机载 EKF 输出不同源</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
+        <x:v>/ekf/ekf_odom</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>nav_msgs/Odometry</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>ekf</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>planner / operator</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>查看融合 odom</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
+        <x:v>rostopic echo -n 1 /ekf/ekf_odom</x:v>
+      </x:c>
+      <x:c r="G11" s="3" t="str">
+        <x:v>LIO 主链下的核心定位输出</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
+        <x:v>/laserMapping/odometry</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>nav_msgs/Odometry</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>faster_lio</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>ekf / operator</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>查看雷达 odom</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
+        <x:v>rostopic echo -n 1 /laserMapping/odometry</x:v>
+      </x:c>
+      <x:c r="G12" s="3" t="str">
+        <x:v>ekf 会依赖它</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>/laserMapping/cloud_registered</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="str">
+        <x:v>sensor_msgs/PointCloud2</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>faster_lio</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>planner / rviz</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
+        <x:v>查看规划输入点云</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="str">
+        <x:v>rostopic hz /laserMapping/cloud_registered</x:v>
+      </x:c>
+      <x:c r="G13" s="3" t="str">
+        <x:v>rviz 观察质量时重点看它</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>/vins/imu_propagate</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="str">
+        <x:v>nav_msgs/Odometry</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>vins</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="str">
+        <x:v>planner / operator</x:v>
+      </x:c>
+      <x:c r="E14" s="3" t="str">
+        <x:v>查看视觉惯性 odom</x:v>
+      </x:c>
+      <x:c r="F14" s="3" t="str">
+        <x:v>rostopic echo -n 1 /vins/imu_propagate</x:v>
+      </x:c>
+      <x:c r="G14" s="3" t="str">
+        <x:v>当前视觉定位主输出</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="15" t="str">
+        <x:v>/drone_0_planning/trajectory</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="str">
+        <x:v>traj_utils/PolyTraj</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="str">
+        <x:v>traj_server</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="str">
+        <x:v>operator / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="str">
+        <x:v>查看当前规划结果</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="str">
+        <x:v>rostopic echo -n 1 /drone_0_planning/trajectory</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="str">
+        <x:v>轨迹有了不等于控制器一定执行</x:v>
+      </x:c>
+      <x:c r="H15" s="17" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23.93000030517578" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28.829999923706055" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28.829999923706055" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>动作接口</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这是当前机器最适合上层系统直接调用的动作原语层。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>动作接口</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>接口</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>输入格式</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>方向</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>前置条件</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>作用</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="str">
+        <x:v>风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>/px4ctrl/takeoff_land</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>quadrotor_msgs/TakeoffLand</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>px4ctrl 与定位链正常</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>起飞与降落动作原语</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>rostopic pub -1 /px4ctrl/takeoff_land quadrotor_msgs/TakeoffLand 'takeoff_land_cmd: 1'</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str">
+        <x:v>RC 档位不对会被拒绝</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>/move_base_simple/goal</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>multipoint 启动且 start_plan=1</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>开始执行点位任务</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="str">
+        <x:v>rostopic pub -1 /move_base_simple/goal geometry_msgs/PoseStamped '{}'</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
+        <x:v>不要和 RC 八通重复发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>/back_trigger</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>multipoint 启动且 back_plan=1</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>开始返程任务</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="str">
+        <x:v>rostopic pub -1 /back_trigger geometry_msgs/PoseStamped '{}'</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>返回路径依赖 test_back</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>/goal</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>任务已启动</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>逐个向规划器发目标点</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="str">
+        <x:v>由 multipoint 自动发布</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>通常不建议外部直接绕过 multipoint 写它</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>/planning/yaw</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>quadrotor_msgs/PositionCommand</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>使用 test3 或 test4</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>按航点注入 yaw</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
+        <x:v>由 multipoint 自动发布</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>VIO 模式不建议使用自定义 yaw</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="15" t="str">
+        <x:v>/setpoints_cmd</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="str">
+        <x:v>quadrotor_msgs/PositionCommand</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="str">
+        <x:v>publish / subscribe</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="str">
+        <x:v>planner 与 px4ctrl 同时存在</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="str">
+        <x:v>规划器给控制器的核心命令通道</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="str">
+        <x:v>内部 remap 到 /setpoints_cmd</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="str">
+        <x:v>高风险接口 不要先从这里直接接上层系统</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="31.290000915527344" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28.829999923706055" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>脚本入口</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>现场同事真实在用的是脚本入口，这里告诉你每个脚本大致负责什么。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>脚本入口</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>脚本</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>类型/格式</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>关键内容</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>前置条件</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>典型用途</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>run_single_lio.sh</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>bash script</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>mavros, faster_lio, ekf, planner, px4ctrl, multipoint</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>Diff-planner workspace sourced</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>启动单机 LIO 全栈</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>启动慢时不要误判失败</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>run_single_vio.sh</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>bash script</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>mavros, realsense, vins, planner, px4ctrl, multipoint</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>Diff-planner workspace sourced</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>启动单机 VIO 全栈</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>相机起不来时 VIO 全链失效</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>takeoff.sh</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>rostopic pub -1 quadrotor_msgs/TakeoffLand</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>takeoff_land_cmd=1</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>px4ctrl 已启动</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>触发自动起飞</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>RC 状态不满足时 px4ctrl 会拒绝</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>pub_trigger.sh</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>rostopic pub -1 geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>empty pose trigger</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>multipoint 已启动</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>触发开始任务</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>不要与 8 通上拨重复触发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>back.sh</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>rostopic pub -1 geometry_msgs/PoseStamped</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>empty pose trigger</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>multipoint 已启动</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>触发返程</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>不要与 8 通中拨重复触发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="15" t="str">
+        <x:v>land.sh</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="str">
+        <x:v>rostopic pub -1 quadrotor_msgs/TakeoffLand</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="str">
+        <x:v>takeoff_land_cmd=2</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="str">
+        <x:v>px4ctrl 已启动</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="str">
+        <x:v>触发自动降落</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="str">
+        <x:v>与 takeoff.sh 共用同一 topic</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23.93000030517578" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23.93000030517578" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28.829999923706055" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>参数入口</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>如果你是来改行为，不是来重写系统，那先看这些文件。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>参数入口</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>文件</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>格式</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>关键参数</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>作用</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>典型用法</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>points.yaml</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>yaml</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>test1 test2 test3 test4 test_back</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>定义任务点和返程点</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>src/user_command/multipoint/config/points.yaml</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>数组长度错会直接读取失败</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>ctrl_param_fpv.yaml</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>yaml</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>low_voltage takeoff_height takeoff_land_speed</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>控制起飞高度和电池阈值</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>src/realflight_modules/px4ctrl/config/ctrl_param_fpv.yaml</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>改前必须确认起飞高度范围无障碍</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>multipointplan_exp_lio.launch</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>roslaunch args</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>fligt_type next_distance start_plan back_plan</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>选择航点模式和触发行为</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>roslaunch multipoint multipointplan_exp_lio.launch</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>fligt_type 拼写就是源码现状 不要擅自改名</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>run_exp_single_lio.launch</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>roslaunch args</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>max_vel max_acc map_resolution flight_type</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>配置 LIO 规划参数</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>roslaunch diff_planner run_exp_single_lio.launch</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>是规划参数不是飞控参数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="15" t="str">
+        <x:v>run_exp_single_vio.launch</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="str">
+        <x:v>roslaunch args</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="str">
+        <x:v>cx cy fx fy max_vel max_acc</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="str">
+        <x:v>配置 VIO 规划参数</x:v>
+      </x:c>
+      <x:c r="E10" s="16" t="str">
+        <x:v>roslaunch diff_planner run_exp_single_vio.launch</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="str">
+        <x:v>视觉内参错误会直接破坏 VIO 规划</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15.34000015258789" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23.93000030517578" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28.829999923706055" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>RC映射</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>开发时一定要把 RC 当作安全边界，而不是背景信息。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>遥控器映射</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>通道</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>输入类型</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>含义</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
+        <x:v>下游</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="str">
+        <x:v>典型用途</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="str">
+        <x:v>风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>RC Channel 5</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>remote control</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>光流 / 姿态 / onboard</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>PX4 / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>切换飞行模式</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>软件控制会被它打断</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>RC Channel 6</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>remote control</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>悬停 / 轨迹</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>PX4 / px4ctrl</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>切换悬停与轨迹控制</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>异常时上拨 6 通是重要兜底</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>RC Channel 7</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>remote control</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>解锁 / 锁桨 / 急停</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>PX4</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>电机安全控制</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>最高安全优先级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="15" t="str">
+        <x:v>RC Channel 8</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>remote control</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>下-&gt;中 takeoff 中-&gt;上 start 上-&gt;中 back 中-&gt;下 land</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="str">
+        <x:v>multipoint / PX4</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="str">
+        <x:v>任务动作触发</x:v>
+      </x:c>
+      <x:c r="F9" s="17" t="str">
+        <x:v>脚本与 RC 触发方式不要混用</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9.199999809265137" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.65999984741211" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="19.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="21.469999313354492" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="26.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="31.290000915527344" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>完整原表</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
+      <x:c r="J1" s="2"/>
+      <x:c r="K1" s="2"/>
+      <x:c r="L1" s="2"/>
+      <x:c r="M1" s="2"/>
+      <x:c r="N1" s="2"/>
+      <x:c r="O1" s="2"/>
+      <x:c r="P1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="str">
+        <x:v>这里保留全部原始字段，用于追溯和查证。</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+      <x:c r="H2" s="4"/>
+      <x:c r="I2" s="4"/>
+      <x:c r="J2" s="4"/>
+      <x:c r="K2" s="4"/>
+      <x:c r="L2" s="4"/>
+      <x:c r="M2" s="4"/>
+      <x:c r="N2" s="4"/>
+      <x:c r="O2" s="4"/>
+      <x:c r="P2" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>完整原表</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
+      <x:c r="I4" s="6"/>
+      <x:c r="J4" s="6"/>
+      <x:c r="K4" s="6"/>
+      <x:c r="L4" s="6"/>
+      <x:c r="M4" s="6"/>
+      <x:c r="N4" s="6"/>
+      <x:c r="O4" s="6"/>
+      <x:c r="P4" s="6"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B1" t="str">
+      <x:c r="B5" s="9" t="str">
         <x:v>category</x:v>
       </x:c>
-      <x:c r="C1" t="str">
+      <x:c r="C5" s="9" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="D5" s="9" t="str">
         <x:v>type</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="E5" s="9" t="str">
         <x:v>direction</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="F5" s="9" t="str">
         <x:v>message_or_format</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="G5" s="9" t="str">
         <x:v>key_fields</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="H5" s="9" t="str">
         <x:v>upstream</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="I5" s="9" t="str">
         <x:v>downstream</x:v>
       </x:c>
-      <x:c r="J1" t="str">
+      <x:c r="J5" s="9" t="str">
         <x:v>preconditions</x:v>
       </x:c>
-      <x:c r="K1" t="str">
+      <x:c r="K5" s="9" t="str">
         <x:v>typical_use</x:v>
       </x:c>
-      <x:c r="L1" t="str">
+      <x:c r="L5" s="9" t="str">
         <x:v>example</x:v>
       </x:c>
-      <x:c r="M1" t="str">
+      <x:c r="M5" s="9" t="str">
         <x:v>machine_status</x:v>
       </x:c>
-      <x:c r="N1" t="str">
+      <x:c r="N5" s="9" t="str">
         <x:v>risks</x:v>
       </x:c>
-      <x:c r="O1" t="str">
+      <x:c r="O5" s="9" t="str">
         <x:v>evidence_id</x:v>
       </x:c>
-      <x:c r="P1" t="str">
+      <x:c r="P5" s="9" t="str">
         <x:v>source_path</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
         <x:v>I001</x:v>
       </x:c>
-      <x:c r="B2" t="str">
+      <x:c r="B6" s="11" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C2" t="str">
+      <x:c r="C6" s="11" t="str">
         <x:v>run_single_lio.sh</x:v>
       </x:c>
-      <x:c r="D2" t="str">
+      <x:c r="D6" s="11" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E2" t="str">
+      <x:c r="E6" s="11" t="str">
         <x:v>entrypoint</x:v>
       </x:c>
-      <x:c r="F2" t="str">
+      <x:c r="F6" s="11" t="str">
         <x:v>bash script</x:v>
       </x:c>
-      <x:c r="G2" t="str">
+      <x:c r="G6" s="11" t="str">
         <x:v>mavros, faster_lio, ekf, planner, px4ctrl, multipoint</x:v>
       </x:c>
-      <x:c r="H2" t="str">
+      <x:c r="H6" s="11" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I2" t="str">
+      <x:c r="I6" s="11" t="str">
         <x:v>ROS graph</x:v>
       </x:c>
-      <x:c r="J2" t="str">
+      <x:c r="J6" s="11" t="str">
         <x:v>Diff-planner workspace sourced</x:v>
       </x:c>
-      <x:c r="K2" t="str">
+      <x:c r="K6" s="11" t="str">
         <x:v>启动单机 LIO 全栈</x:v>
       </x:c>
-      <x:c r="L2" t="str">
-        <x:v>cd ~/Diff-Planner &amp;&amp; ./sh_files/run_single_lio.sh</x:v>
-      </x:c>
-      <x:c r="M2" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N2" t="str">
+      <x:c r="L6" s="11" t="str">
+        <x:v>cd ~/Diff-planner &amp;&amp; ./sh_files/run_single_lio.sh</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N6" s="11" t="str">
         <x:v>启动慢时不要误判失败</x:v>
       </x:c>
-      <x:c r="O2" t="str">
+      <x:c r="O6" s="11" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
-      <x:c r="P2" t="str">
+      <x:c r="P6" s="12" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/run_single_lio.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
         <x:v>I002</x:v>
       </x:c>
-      <x:c r="B3" t="str">
+      <x:c r="B7" s="3" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C3" t="str">
+      <x:c r="C7" s="3" t="str">
         <x:v>run_single_vio.sh</x:v>
       </x:c>
-      <x:c r="D3" t="str">
+      <x:c r="D7" s="3" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E3" t="str">
+      <x:c r="E7" s="3" t="str">
         <x:v>entrypoint</x:v>
       </x:c>
-      <x:c r="F3" t="str">
+      <x:c r="F7" s="3" t="str">
         <x:v>bash script</x:v>
       </x:c>
-      <x:c r="G3" t="str">
+      <x:c r="G7" s="3" t="str">
         <x:v>mavros, realsense, vins, planner, px4ctrl, multipoint</x:v>
       </x:c>
-      <x:c r="H3" t="str">
+      <x:c r="H7" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I3" t="str">
+      <x:c r="I7" s="3" t="str">
         <x:v>ROS graph</x:v>
       </x:c>
-      <x:c r="J3" t="str">
+      <x:c r="J7" s="3" t="str">
         <x:v>Diff-planner workspace sourced</x:v>
       </x:c>
-      <x:c r="K3" t="str">
+      <x:c r="K7" s="3" t="str">
         <x:v>启动单机 VIO 全栈</x:v>
       </x:c>
-      <x:c r="L3" t="str">
-        <x:v>cd ~/Diff-Planner &amp;&amp; ./sh_files/run_single_vio.sh</x:v>
-      </x:c>
-      <x:c r="M3" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N3" t="str">
+      <x:c r="L7" s="3" t="str">
+        <x:v>cd ~/Diff-planner &amp;&amp; ./sh_files/run_single_vio.sh</x:v>
+      </x:c>
+      <x:c r="M7" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N7" s="3" t="str">
         <x:v>相机起不来时 VIO 全链失效</x:v>
       </x:c>
-      <x:c r="O3" t="str">
+      <x:c r="O7" s="3" t="str">
         <x:v>E007_run_single_vio_script</x:v>
       </x:c>
-      <x:c r="P3" t="str">
+      <x:c r="P7" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/run_single_vio.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
         <x:v>I003</x:v>
       </x:c>
-      <x:c r="B4" t="str">
+      <x:c r="B8" s="3" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C4" t="str">
+      <x:c r="C8" s="3" t="str">
         <x:v>takeoff.sh</x:v>
       </x:c>
-      <x:c r="D4" t="str">
+      <x:c r="D8" s="3" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E4" t="str">
+      <x:c r="E8" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F4" t="str">
+      <x:c r="F8" s="3" t="str">
         <x:v>rostopic pub -1 quadrotor_msgs/TakeoffLand</x:v>
       </x:c>
-      <x:c r="G4" t="str">
+      <x:c r="G8" s="3" t="str">
         <x:v>takeoff_land_cmd=1</x:v>
       </x:c>
-      <x:c r="H4" t="str">
+      <x:c r="H8" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I4" t="str">
+      <x:c r="I8" s="3" t="str">
         <x:v>/px4ctrl/takeoff_land</x:v>
       </x:c>
-      <x:c r="J4" t="str">
+      <x:c r="J8" s="3" t="str">
         <x:v>px4ctrl 已启动</x:v>
       </x:c>
-      <x:c r="K4" t="str">
+      <x:c r="K8" s="3" t="str">
         <x:v>触发自动起飞</x:v>
       </x:c>
-      <x:c r="L4" t="str">
+      <x:c r="L8" s="3" t="str">
         <x:v>./sh_files/takeoff.sh</x:v>
       </x:c>
-      <x:c r="M4" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N4" t="str">
+      <x:c r="M8" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N8" s="3" t="str">
         <x:v>RC 状态不满足时 px4ctrl 会拒绝</x:v>
       </x:c>
-      <x:c r="O4" t="str">
+      <x:c r="O8" s="3" t="str">
         <x:v>E008_takeoff_topic</x:v>
       </x:c>
-      <x:c r="P4" t="str">
+      <x:c r="P8" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/takeoff.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
         <x:v>I004</x:v>
       </x:c>
-      <x:c r="B5" t="str">
+      <x:c r="B9" s="3" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C5" t="str">
+      <x:c r="C9" s="3" t="str">
         <x:v>pub_trigger.sh</x:v>
       </x:c>
-      <x:c r="D5" t="str">
+      <x:c r="D9" s="3" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E5" t="str">
+      <x:c r="E9" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F5" t="str">
+      <x:c r="F9" s="3" t="str">
         <x:v>rostopic pub -1 geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G5" t="str">
+      <x:c r="G9" s="3" t="str">
         <x:v>empty pose trigger</x:v>
       </x:c>
-      <x:c r="H5" t="str">
+      <x:c r="H9" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I5" t="str">
+      <x:c r="I9" s="3" t="str">
         <x:v>/move_base_simple/goal</x:v>
       </x:c>
-      <x:c r="J5" t="str">
+      <x:c r="J9" s="3" t="str">
         <x:v>multipoint 已启动</x:v>
       </x:c>
-      <x:c r="K5" t="str">
+      <x:c r="K9" s="3" t="str">
         <x:v>触发开始任务</x:v>
       </x:c>
-      <x:c r="L5" t="str">
+      <x:c r="L9" s="3" t="str">
         <x:v>./sh_files/pub_trigger.sh</x:v>
       </x:c>
-      <x:c r="M5" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N5" t="str">
+      <x:c r="M9" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N9" s="3" t="str">
         <x:v>不要与 8 通上拨重复触发</x:v>
       </x:c>
-      <x:c r="O5" t="str">
+      <x:c r="O9" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P5" t="str">
+      <x:c r="P9" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/pub_trigger.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
         <x:v>I005</x:v>
       </x:c>
-      <x:c r="B6" t="str">
+      <x:c r="B10" s="3" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C6" t="str">
+      <x:c r="C10" s="3" t="str">
         <x:v>back.sh</x:v>
       </x:c>
-      <x:c r="D6" t="str">
+      <x:c r="D10" s="3" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E6" t="str">
+      <x:c r="E10" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F6" t="str">
+      <x:c r="F10" s="3" t="str">
         <x:v>rostopic pub -1 geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G6" t="str">
+      <x:c r="G10" s="3" t="str">
         <x:v>empty pose trigger</x:v>
       </x:c>
-      <x:c r="H6" t="str">
+      <x:c r="H10" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I6" t="str">
+      <x:c r="I10" s="3" t="str">
         <x:v>/back_trigger</x:v>
       </x:c>
-      <x:c r="J6" t="str">
+      <x:c r="J10" s="3" t="str">
         <x:v>multipoint 已启动</x:v>
       </x:c>
-      <x:c r="K6" t="str">
+      <x:c r="K10" s="3" t="str">
         <x:v>触发返程</x:v>
       </x:c>
-      <x:c r="L6" t="str">
+      <x:c r="L10" s="3" t="str">
         <x:v>./sh_files/back.sh</x:v>
       </x:c>
-      <x:c r="M6" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N6" t="str">
+      <x:c r="M10" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N10" s="3" t="str">
         <x:v>不要与 8 通中拨重复触发</x:v>
       </x:c>
-      <x:c r="O6" t="str">
+      <x:c r="O10" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P6" t="str">
+      <x:c r="P10" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/back.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
+    <x:row r="11">
+      <x:c r="A11" s="13" t="str">
         <x:v>I006</x:v>
       </x:c>
-      <x:c r="B7" t="str">
+      <x:c r="B11" s="3" t="str">
         <x:v>script</x:v>
       </x:c>
-      <x:c r="C7" t="str">
+      <x:c r="C11" s="3" t="str">
         <x:v>land.sh</x:v>
       </x:c>
-      <x:c r="D7" t="str">
+      <x:c r="D11" s="3" t="str">
         <x:v>shell</x:v>
       </x:c>
-      <x:c r="E7" t="str">
+      <x:c r="E11" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F7" t="str">
+      <x:c r="F11" s="3" t="str">
         <x:v>rostopic pub -1 quadrotor_msgs/TakeoffLand</x:v>
       </x:c>
-      <x:c r="G7" t="str">
+      <x:c r="G11" s="3" t="str">
         <x:v>takeoff_land_cmd=2</x:v>
       </x:c>
-      <x:c r="H7" t="str">
+      <x:c r="H11" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I7" t="str">
+      <x:c r="I11" s="3" t="str">
         <x:v>/px4ctrl/takeoff_land</x:v>
       </x:c>
-      <x:c r="J7" t="str">
+      <x:c r="J11" s="3" t="str">
         <x:v>px4ctrl 已启动</x:v>
       </x:c>
-      <x:c r="K7" t="str">
+      <x:c r="K11" s="3" t="str">
         <x:v>触发自动降落</x:v>
       </x:c>
-      <x:c r="L7" t="str">
+      <x:c r="L11" s="3" t="str">
         <x:v>./sh_files/land.sh</x:v>
       </x:c>
-      <x:c r="M7" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N7" t="str">
+      <x:c r="M11" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N11" s="3" t="str">
         <x:v>与 takeoff.sh 共用同一 topic</x:v>
       </x:c>
-      <x:c r="O7" t="str">
+      <x:c r="O11" s="3" t="str">
         <x:v>E008_takeoff_topic</x:v>
       </x:c>
-      <x:c r="P7" t="str">
+      <x:c r="P11" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/land.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
+    <x:row r="12">
+      <x:c r="A12" s="13" t="str">
         <x:v>I007</x:v>
       </x:c>
-      <x:c r="B8" t="str">
+      <x:c r="B12" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C8" t="str">
+      <x:c r="C12" s="3" t="str">
         <x:v>/px4ctrl/takeoff_land</x:v>
       </x:c>
-      <x:c r="D8" t="str">
+      <x:c r="D12" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E8" t="str">
+      <x:c r="E12" s="3" t="str">
         <x:v>publish / subscribe</x:v>
       </x:c>
-      <x:c r="F8" t="str">
+      <x:c r="F12" s="3" t="str">
         <x:v>quadrotor_msgs/TakeoffLand</x:v>
       </x:c>
-      <x:c r="G8" t="str">
+      <x:c r="G12" s="3" t="str">
         <x:v>takeoff_land_cmd={1 takeoff,2 land}</x:v>
       </x:c>
-      <x:c r="H8" t="str">
+      <x:c r="H12" s="3" t="str">
         <x:v>script or RC bridge</x:v>
       </x:c>
-      <x:c r="I8" t="str">
+      <x:c r="I12" s="3" t="str">
         <x:v>px4ctrl</x:v>
       </x:c>
-      <x:c r="J8" t="str">
+      <x:c r="J12" s="3" t="str">
         <x:v>px4ctrl 与定位链正常</x:v>
       </x:c>
-      <x:c r="K8" t="str">
+      <x:c r="K12" s="3" t="str">
         <x:v>起飞与降落动作原语</x:v>
       </x:c>
-      <x:c r="L8" t="str">
+      <x:c r="L12" s="3" t="str">
         <x:v>rostopic pub -1 /px4ctrl/takeoff_land quadrotor_msgs/TakeoffLand 'takeoff_land_cmd: 1'</x:v>
       </x:c>
-      <x:c r="M8" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N8" t="str">
+      <x:c r="M12" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N12" s="3" t="str">
         <x:v>RC 档位不对会被拒绝</x:v>
       </x:c>
-      <x:c r="O8" t="str">
+      <x:c r="O12" s="3" t="str">
         <x:v>E008_takeoff_topic</x:v>
       </x:c>
-      <x:c r="P8" t="str">
+      <x:c r="P12" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/sh_files/takeoff.sh</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
         <x:v>I008</x:v>
       </x:c>
-      <x:c r="B9" t="str">
+      <x:c r="B13" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C9" t="str">
+      <x:c r="C13" s="3" t="str">
         <x:v>/move_base_simple/goal</x:v>
       </x:c>
-      <x:c r="D9" t="str">
+      <x:c r="D13" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E9" t="str">
+      <x:c r="E13" s="3" t="str">
         <x:v>publish / subscribe</x:v>
       </x:c>
-      <x:c r="F9" t="str">
+      <x:c r="F13" s="3" t="str">
         <x:v>geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G9" t="str">
+      <x:c r="G13" s="3" t="str">
         <x:v>header stamp only is sufficient for trigger</x:v>
       </x:c>
-      <x:c r="H9" t="str">
+      <x:c r="H13" s="3" t="str">
         <x:v>script or RC bridge</x:v>
       </x:c>
-      <x:c r="I9" t="str">
+      <x:c r="I13" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="J9" t="str">
+      <x:c r="J13" s="3" t="str">
         <x:v>multipoint 启动且 start_plan=1</x:v>
       </x:c>
-      <x:c r="K9" t="str">
+      <x:c r="K13" s="3" t="str">
         <x:v>开始执行点位任务</x:v>
       </x:c>
-      <x:c r="L9" t="str">
+      <x:c r="L13" s="3" t="str">
         <x:v>rostopic pub -1 /move_base_simple/goal geometry_msgs/PoseStamped '{}'</x:v>
       </x:c>
-      <x:c r="M9" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N9" t="str">
+      <x:c r="M13" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N13" s="3" t="str">
         <x:v>不要和 RC 八通重复发</x:v>
       </x:c>
-      <x:c r="O9" t="str">
+      <x:c r="O13" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P9" t="str">
+      <x:c r="P13" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
         <x:v>I009</x:v>
       </x:c>
-      <x:c r="B10" t="str">
+      <x:c r="B14" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C10" t="str">
+      <x:c r="C14" s="3" t="str">
         <x:v>/back_trigger</x:v>
       </x:c>
-      <x:c r="D10" t="str">
+      <x:c r="D14" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E10" t="str">
+      <x:c r="E14" s="3" t="str">
         <x:v>publish / subscribe</x:v>
       </x:c>
-      <x:c r="F10" t="str">
+      <x:c r="F14" s="3" t="str">
         <x:v>geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G10" t="str">
+      <x:c r="G14" s="3" t="str">
         <x:v>header stamp only is sufficient for trigger</x:v>
       </x:c>
-      <x:c r="H10" t="str">
+      <x:c r="H14" s="3" t="str">
         <x:v>script or RC bridge</x:v>
       </x:c>
-      <x:c r="I10" t="str">
+      <x:c r="I14" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="J10" t="str">
+      <x:c r="J14" s="3" t="str">
         <x:v>multipoint 启动且 back_plan=1</x:v>
       </x:c>
-      <x:c r="K10" t="str">
+      <x:c r="K14" s="3" t="str">
         <x:v>开始返程任务</x:v>
       </x:c>
-      <x:c r="L10" t="str">
+      <x:c r="L14" s="3" t="str">
         <x:v>rostopic pub -1 /back_trigger geometry_msgs/PoseStamped '{}'</x:v>
       </x:c>
-      <x:c r="M10" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N10" t="str">
+      <x:c r="M14" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N14" s="3" t="str">
         <x:v>返回路径依赖 test_back</x:v>
       </x:c>
-      <x:c r="O10" t="str">
+      <x:c r="O14" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P10" t="str">
+      <x:c r="P14" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
         <x:v>I010</x:v>
       </x:c>
-      <x:c r="B11" t="str">
+      <x:c r="B15" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C11" t="str">
+      <x:c r="C15" s="3" t="str">
         <x:v>/goal</x:v>
       </x:c>
-      <x:c r="D11" t="str">
+      <x:c r="D15" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E11" t="str">
+      <x:c r="E15" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F11" t="str">
+      <x:c r="F15" s="3" t="str">
         <x:v>geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G11" t="str">
+      <x:c r="G15" s="3" t="str">
         <x:v>position xyz</x:v>
       </x:c>
-      <x:c r="H11" t="str">
+      <x:c r="H15" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="I11" t="str">
+      <x:c r="I15" s="3" t="str">
         <x:v>planner</x:v>
       </x:c>
-      <x:c r="J11" t="str">
+      <x:c r="J15" s="3" t="str">
         <x:v>任务已启动</x:v>
       </x:c>
-      <x:c r="K11" t="str">
+      <x:c r="K15" s="3" t="str">
         <x:v>逐个向规划器发目标点</x:v>
       </x:c>
-      <x:c r="L11" t="str">
+      <x:c r="L15" s="3" t="str">
         <x:v>由 multipoint 自动发布</x:v>
       </x:c>
-      <x:c r="M11" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N11" t="str">
+      <x:c r="M15" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N15" s="3" t="str">
         <x:v>通常不建议外部直接绕过 multipoint 写它</x:v>
       </x:c>
-      <x:c r="O11" t="str">
+      <x:c r="O15" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P11" t="str">
+      <x:c r="P15" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
         <x:v>I011</x:v>
       </x:c>
-      <x:c r="B12" t="str">
+      <x:c r="B16" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C12" t="str">
+      <x:c r="C16" s="3" t="str">
         <x:v>/planning/yaw</x:v>
       </x:c>
-      <x:c r="D12" t="str">
+      <x:c r="D16" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E12" t="str">
+      <x:c r="E16" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F12" t="str">
+      <x:c r="F16" s="3" t="str">
         <x:v>quadrotor_msgs/PositionCommand</x:v>
       </x:c>
-      <x:c r="G12" t="str">
+      <x:c r="G16" s="3" t="str">
         <x:v>yaw</x:v>
       </x:c>
-      <x:c r="H12" t="str">
+      <x:c r="H16" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="I12" t="str">
+      <x:c r="I16" s="3" t="str">
         <x:v>planner</x:v>
       </x:c>
-      <x:c r="J12" t="str">
+      <x:c r="J16" s="3" t="str">
         <x:v>使用 test3 或 test4</x:v>
       </x:c>
-      <x:c r="K12" t="str">
+      <x:c r="K16" s="3" t="str">
         <x:v>按航点注入 yaw</x:v>
       </x:c>
-      <x:c r="L12" t="str">
+      <x:c r="L16" s="3" t="str">
         <x:v>由 multipoint 自动发布</x:v>
       </x:c>
-      <x:c r="M12" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N12" t="str">
+      <x:c r="M16" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N16" s="3" t="str">
         <x:v>VIO 模式不建议使用自定义 yaw</x:v>
       </x:c>
-      <x:c r="O12" t="str">
+      <x:c r="O16" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P12" t="str">
+      <x:c r="P16" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
         <x:v>I012</x:v>
       </x:c>
-      <x:c r="B13" t="str">
+      <x:c r="B17" s="3" t="str">
         <x:v>action</x:v>
       </x:c>
-      <x:c r="C13" t="str">
+      <x:c r="C17" s="3" t="str">
         <x:v>/setpoints_cmd</x:v>
       </x:c>
-      <x:c r="D13" t="str">
+      <x:c r="D17" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E13" t="str">
+      <x:c r="E17" s="3" t="str">
         <x:v>publish / subscribe</x:v>
       </x:c>
-      <x:c r="F13" t="str">
+      <x:c r="F17" s="3" t="str">
         <x:v>quadrotor_msgs/PositionCommand</x:v>
       </x:c>
-      <x:c r="G13" t="str">
+      <x:c r="G17" s="3" t="str">
         <x:v>position velocity acceleration yaw</x:v>
       </x:c>
-      <x:c r="H13" t="str">
+      <x:c r="H17" s="3" t="str">
         <x:v>traj_server</x:v>
       </x:c>
-      <x:c r="I13" t="str">
+      <x:c r="I17" s="3" t="str">
         <x:v>px4ctrl</x:v>
       </x:c>
-      <x:c r="J13" t="str">
+      <x:c r="J17" s="3" t="str">
         <x:v>planner 与 px4ctrl 同时存在</x:v>
       </x:c>
-      <x:c r="K13" t="str">
+      <x:c r="K17" s="3" t="str">
         <x:v>规划器给控制器的核心命令通道</x:v>
       </x:c>
-      <x:c r="L13" t="str">
+      <x:c r="L17" s="3" t="str">
         <x:v>内部 remap 到 /setpoints_cmd</x:v>
       </x:c>
-      <x:c r="M13" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N13" t="str">
+      <x:c r="M17" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N17" s="3" t="str">
         <x:v>高风险接口 不要先从这里直接接上层系统</x:v>
       </x:c>
-      <x:c r="O13" t="str">
+      <x:c r="O17" s="3" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
-      <x:c r="P13" t="str">
+      <x:c r="P17" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/realflight_modules/px4ctrl/launch/run_ctrl_lio.launch</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
+    <x:row r="18">
+      <x:c r="A18" s="13" t="str">
         <x:v>I013</x:v>
       </x:c>
-      <x:c r="B14" t="str">
+      <x:c r="B18" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C14" t="str">
+      <x:c r="C18" s="3" t="str">
         <x:v>/mavros/state</x:v>
       </x:c>
-      <x:c r="D14" t="str">
+      <x:c r="D18" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E14" t="str">
+      <x:c r="E18" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F14" t="str">
+      <x:c r="F18" s="3" t="str">
         <x:v>mavros_msgs/State</x:v>
       </x:c>
-      <x:c r="G14" t="str">
+      <x:c r="G18" s="3" t="str">
         <x:v>connected armed mode</x:v>
       </x:c>
-      <x:c r="H14" t="str">
+      <x:c r="H18" s="3" t="str">
         <x:v>mavros</x:v>
       </x:c>
-      <x:c r="I14" t="str">
+      <x:c r="I18" s="3" t="str">
         <x:v>operator / px4ctrl</x:v>
       </x:c>
-      <x:c r="J14" t="str">
+      <x:c r="J18" s="3" t="str">
         <x:v>mavros 已启动</x:v>
       </x:c>
-      <x:c r="K14" t="str">
+      <x:c r="K18" s="3" t="str">
         <x:v>查看飞控连接与模式</x:v>
       </x:c>
-      <x:c r="L14" t="str">
+      <x:c r="L18" s="3" t="str">
         <x:v>rostopic echo -n 1 /mavros/state</x:v>
       </x:c>
-      <x:c r="M14" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N14" t="str">
+      <x:c r="M18" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N18" s="3" t="str">
         <x:v>最先判断 FCU 是否连上</x:v>
       </x:c>
-      <x:c r="O14" t="str">
+      <x:c r="O18" s="3" t="str">
         <x:v>E013_battery_topic</x:v>
       </x:c>
-      <x:c r="P14" t="str">
+      <x:c r="P18" s="14" t="str">
         <x:v>uav/10-knowledge-base/06-指令速查-含隐藏命令.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
+    <x:row r="19">
+      <x:c r="A19" s="13" t="str">
         <x:v>I014</x:v>
       </x:c>
-      <x:c r="B15" t="str">
+      <x:c r="B19" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C15" t="str">
+      <x:c r="C19" s="3" t="str">
         <x:v>/mavros/battery</x:v>
       </x:c>
-      <x:c r="D15" t="str">
+      <x:c r="D19" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E15" t="str">
+      <x:c r="E19" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F15" t="str">
+      <x:c r="F19" s="3" t="str">
         <x:v>sensor_msgs/BatteryState</x:v>
       </x:c>
-      <x:c r="G15" t="str">
+      <x:c r="G19" s="3" t="str">
         <x:v>voltage percentage current</x:v>
       </x:c>
-      <x:c r="H15" t="str">
+      <x:c r="H19" s="3" t="str">
         <x:v>mavros</x:v>
       </x:c>
-      <x:c r="I15" t="str">
+      <x:c r="I19" s="3" t="str">
         <x:v>operator / px4ctrl</x:v>
       </x:c>
-      <x:c r="J15" t="str">
+      <x:c r="J19" s="3" t="str">
         <x:v>mavros 已启动</x:v>
       </x:c>
-      <x:c r="K15" t="str">
+      <x:c r="K19" s="3" t="str">
         <x:v>查看电量</x:v>
       </x:c>
-      <x:c r="L15" t="str">
+      <x:c r="L19" s="3" t="str">
         <x:v>rostopic echo -n 1 /mavros/battery</x:v>
       </x:c>
-      <x:c r="M15" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N15" t="str">
+      <x:c r="M19" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N19" s="3" t="str">
         <x:v>低压阈值与 ctrl_param_fpv.yaml 联动</x:v>
       </x:c>
-      <x:c r="O15" t="str">
+      <x:c r="O19" s="3" t="str">
         <x:v>E013_battery_topic</x:v>
       </x:c>
-      <x:c r="P15" t="str">
+      <x:c r="P19" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str">
+    <x:row r="20">
+      <x:c r="A20" s="13" t="str">
         <x:v>I015</x:v>
       </x:c>
-      <x:c r="B16" t="str">
+      <x:c r="B20" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C16" t="str">
+      <x:c r="C20" s="3" t="str">
         <x:v>/mavros/rc/in</x:v>
       </x:c>
-      <x:c r="D16" t="str">
+      <x:c r="D20" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E16" t="str">
+      <x:c r="E20" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F16" t="str">
+      <x:c r="F20" s="3" t="str">
         <x:v>mavros_msgs/RCIn</x:v>
       </x:c>
-      <x:c r="G16" t="str">
+      <x:c r="G20" s="3" t="str">
         <x:v>channels[0..]</x:v>
       </x:c>
-      <x:c r="H16" t="str">
+      <x:c r="H20" s="3" t="str">
         <x:v>mavros</x:v>
       </x:c>
-      <x:c r="I16" t="str">
+      <x:c r="I20" s="3" t="str">
         <x:v>multipoint / px4ctrl</x:v>
       </x:c>
-      <x:c r="J16" t="str">
+      <x:c r="J20" s="3" t="str">
         <x:v>mavros 已启动且 RC 在线</x:v>
       </x:c>
-      <x:c r="K16" t="str">
+      <x:c r="K20" s="3" t="str">
         <x:v>查看遥控器输入</x:v>
       </x:c>
-      <x:c r="L16" t="str">
+      <x:c r="L20" s="3" t="str">
         <x:v>rostopic echo -n 1 /mavros/rc/in</x:v>
       </x:c>
-      <x:c r="M16" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N16" t="str">
+      <x:c r="M20" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N20" s="3" t="str">
         <x:v>是安全门也是动作触发来源</x:v>
       </x:c>
-      <x:c r="O16" t="str">
+      <x:c r="O20" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P16" t="str">
+      <x:c r="P20" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
+    <x:row r="21">
+      <x:c r="A21" s="13" t="str">
         <x:v>I016</x:v>
       </x:c>
-      <x:c r="B17" t="str">
+      <x:c r="B21" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C17" t="str">
+      <x:c r="C21" s="3" t="str">
         <x:v>/mavros/imu/data</x:v>
       </x:c>
-      <x:c r="D17" t="str">
+      <x:c r="D21" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E17" t="str">
+      <x:c r="E21" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F17" t="str">
+      <x:c r="F21" s="3" t="str">
         <x:v>sensor_msgs/Imu</x:v>
       </x:c>
-      <x:c r="G17" t="str">
+      <x:c r="G21" s="3" t="str">
         <x:v>orientation angular_velocity linear_acceleration</x:v>
       </x:c>
-      <x:c r="H17" t="str">
+      <x:c r="H21" s="3" t="str">
         <x:v>mavros</x:v>
       </x:c>
-      <x:c r="I17" t="str">
+      <x:c r="I21" s="3" t="str">
         <x:v>px4ctrl</x:v>
       </x:c>
-      <x:c r="J17" t="str">
+      <x:c r="J21" s="3" t="str">
         <x:v>mavros 已启动</x:v>
       </x:c>
-      <x:c r="K17" t="str">
+      <x:c r="K21" s="3" t="str">
         <x:v>飞控 IMU 输入</x:v>
       </x:c>
-      <x:c r="L17" t="str">
+      <x:c r="L21" s="3" t="str">
         <x:v>rostopic echo -n 1 /mavros/imu/data</x:v>
       </x:c>
-      <x:c r="M17" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N17" t="str">
+      <x:c r="M21" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N21" s="3" t="str">
         <x:v>px4ctrl 明确使用 data 非 data_raw</x:v>
       </x:c>
-      <x:c r="O17" t="str">
+      <x:c r="O21" s="3" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
-      <x:c r="P17" t="str">
+      <x:c r="P21" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/realflight_modules/px4ctrl/src/px4ctrl_node.cpp</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="str">
+    <x:row r="22">
+      <x:c r="A22" s="13" t="str">
         <x:v>I017</x:v>
       </x:c>
-      <x:c r="B18" t="str">
+      <x:c r="B22" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C18" t="str">
+      <x:c r="C22" s="3" t="str">
         <x:v>/mavros/local_position/pose</x:v>
       </x:c>
-      <x:c r="D18" t="str">
+      <x:c r="D22" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E18" t="str">
+      <x:c r="E22" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F18" t="str">
+      <x:c r="F22" s="3" t="str">
         <x:v>geometry_msgs/PoseStamped</x:v>
       </x:c>
-      <x:c r="G18" t="str">
+      <x:c r="G22" s="3" t="str">
         <x:v>pose</x:v>
       </x:c>
-      <x:c r="H18" t="str">
+      <x:c r="H22" s="3" t="str">
         <x:v>mavros</x:v>
       </x:c>
-      <x:c r="I18" t="str">
+      <x:c r="I22" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="J18" t="str">
+      <x:c r="J22" s="3" t="str">
         <x:v>mavros 已启动</x:v>
       </x:c>
-      <x:c r="K18" t="str">
+      <x:c r="K22" s="3" t="str">
         <x:v>查看 PX4 本地位姿</x:v>
       </x:c>
-      <x:c r="L18" t="str">
+      <x:c r="L22" s="3" t="str">
         <x:v>rostopic echo -n 1 /mavros/local_position/pose</x:v>
       </x:c>
-      <x:c r="M18" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N18" t="str">
+      <x:c r="M22" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N22" s="3" t="str">
         <x:v>与机载 EKF 输出不同源</x:v>
       </x:c>
-      <x:c r="O18" t="str">
+      <x:c r="O22" s="3" t="str">
         <x:v>E013_battery_topic</x:v>
       </x:c>
-      <x:c r="P18" t="str">
+      <x:c r="P22" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
+    <x:row r="23">
+      <x:c r="A23" s="13" t="str">
         <x:v>I018</x:v>
       </x:c>
-      <x:c r="B19" t="str">
+      <x:c r="B23" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C19" t="str">
+      <x:c r="C23" s="3" t="str">
         <x:v>/ekf/ekf_odom</x:v>
       </x:c>
-      <x:c r="D19" t="str">
+      <x:c r="D23" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E19" t="str">
+      <x:c r="E23" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F19" t="str">
+      <x:c r="F23" s="3" t="str">
         <x:v>nav_msgs/Odometry</x:v>
       </x:c>
-      <x:c r="G19" t="str">
+      <x:c r="G23" s="3" t="str">
         <x:v>pose twist</x:v>
       </x:c>
-      <x:c r="H19" t="str">
+      <x:c r="H23" s="3" t="str">
         <x:v>ekf</x:v>
       </x:c>
-      <x:c r="I19" t="str">
+      <x:c r="I23" s="3" t="str">
         <x:v>planner / operator</x:v>
       </x:c>
-      <x:c r="J19" t="str">
+      <x:c r="J23" s="3" t="str">
         <x:v>LIO 主链已启动</x:v>
       </x:c>
-      <x:c r="K19" t="str">
+      <x:c r="K23" s="3" t="str">
         <x:v>查看融合 odom</x:v>
       </x:c>
-      <x:c r="L19" t="str">
+      <x:c r="L23" s="3" t="str">
         <x:v>rostopic echo -n 1 /ekf/ekf_odom</x:v>
       </x:c>
-      <x:c r="M19" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N19" t="str">
+      <x:c r="M23" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N23" s="3" t="str">
         <x:v>LIO 主链下的核心定位输出</x:v>
       </x:c>
-      <x:c r="O19" t="str">
+      <x:c r="O23" s="3" t="str">
         <x:v>E012_ekf_output</x:v>
       </x:c>
-      <x:c r="P19" t="str">
+      <x:c r="P23" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="str">
+    <x:row r="24">
+      <x:c r="A24" s="13" t="str">
         <x:v>I019</x:v>
       </x:c>
-      <x:c r="B20" t="str">
+      <x:c r="B24" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C20" t="str">
+      <x:c r="C24" s="3" t="str">
         <x:v>/laserMapping/odometry</x:v>
       </x:c>
-      <x:c r="D20" t="str">
+      <x:c r="D24" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E20" t="str">
+      <x:c r="E24" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F20" t="str">
+      <x:c r="F24" s="3" t="str">
         <x:v>nav_msgs/Odometry</x:v>
       </x:c>
-      <x:c r="G20" t="str">
+      <x:c r="G24" s="3" t="str">
         <x:v>pose twist</x:v>
       </x:c>
-      <x:c r="H20" t="str">
+      <x:c r="H24" s="3" t="str">
         <x:v>faster_lio</x:v>
       </x:c>
-      <x:c r="I20" t="str">
+      <x:c r="I24" s="3" t="str">
         <x:v>ekf / operator</x:v>
       </x:c>
-      <x:c r="J20" t="str">
+      <x:c r="J24" s="3" t="str">
         <x:v>faster_lio 已启动</x:v>
       </x:c>
-      <x:c r="K20" t="str">
+      <x:c r="K24" s="3" t="str">
         <x:v>查看雷达 odom</x:v>
       </x:c>
-      <x:c r="L20" t="str">
+      <x:c r="L24" s="3" t="str">
         <x:v>rostopic echo -n 1 /laserMapping/odometry</x:v>
       </x:c>
-      <x:c r="M20" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N20" t="str">
+      <x:c r="M24" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N24" s="3" t="str">
         <x:v>ekf 会依赖它</x:v>
       </x:c>
-      <x:c r="O20" t="str">
+      <x:c r="O24" s="3" t="str">
         <x:v>E012_ekf_output</x:v>
       </x:c>
-      <x:c r="P20" t="str">
+      <x:c r="P24" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="str">
+    <x:row r="25">
+      <x:c r="A25" s="13" t="str">
         <x:v>I020</x:v>
       </x:c>
-      <x:c r="B21" t="str">
+      <x:c r="B25" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C21" t="str">
+      <x:c r="C25" s="3" t="str">
         <x:v>/laserMapping/cloud_registered</x:v>
       </x:c>
-      <x:c r="D21" t="str">
+      <x:c r="D25" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E21" t="str">
+      <x:c r="E25" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F21" t="str">
+      <x:c r="F25" s="3" t="str">
         <x:v>sensor_msgs/PointCloud2</x:v>
       </x:c>
-      <x:c r="G21" t="str">
+      <x:c r="G25" s="3" t="str">
         <x:v>point cloud</x:v>
       </x:c>
-      <x:c r="H21" t="str">
+      <x:c r="H25" s="3" t="str">
         <x:v>faster_lio</x:v>
       </x:c>
-      <x:c r="I21" t="str">
+      <x:c r="I25" s="3" t="str">
         <x:v>planner / rviz</x:v>
       </x:c>
-      <x:c r="J21" t="str">
+      <x:c r="J25" s="3" t="str">
         <x:v>faster_lio 已启动</x:v>
       </x:c>
-      <x:c r="K21" t="str">
+      <x:c r="K25" s="3" t="str">
         <x:v>查看规划输入点云</x:v>
       </x:c>
-      <x:c r="L21" t="str">
+      <x:c r="L25" s="3" t="str">
         <x:v>rostopic hz /laserMapping/cloud_registered</x:v>
       </x:c>
-      <x:c r="M21" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N21" t="str">
+      <x:c r="M25" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N25" s="3" t="str">
         <x:v>rviz 观察质量时重点看它</x:v>
       </x:c>
-      <x:c r="O21" t="str">
+      <x:c r="O25" s="3" t="str">
         <x:v>E012_ekf_output</x:v>
       </x:c>
-      <x:c r="P21" t="str">
+      <x:c r="P25" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
+    <x:row r="26">
+      <x:c r="A26" s="13" t="str">
         <x:v>I021</x:v>
       </x:c>
-      <x:c r="B22" t="str">
+      <x:c r="B26" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C22" t="str">
+      <x:c r="C26" s="3" t="str">
         <x:v>/vins/imu_propagate</x:v>
       </x:c>
-      <x:c r="D22" t="str">
+      <x:c r="D26" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E22" t="str">
+      <x:c r="E26" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F22" t="str">
+      <x:c r="F26" s="3" t="str">
         <x:v>nav_msgs/Odometry</x:v>
       </x:c>
-      <x:c r="G22" t="str">
+      <x:c r="G26" s="3" t="str">
         <x:v>pose twist</x:v>
       </x:c>
-      <x:c r="H22" t="str">
+      <x:c r="H26" s="3" t="str">
         <x:v>vins</x:v>
       </x:c>
-      <x:c r="I22" t="str">
+      <x:c r="I26" s="3" t="str">
         <x:v>planner / operator</x:v>
       </x:c>
-      <x:c r="J22" t="str">
+      <x:c r="J26" s="3" t="str">
         <x:v>VIO 主链已启动</x:v>
       </x:c>
-      <x:c r="K22" t="str">
+      <x:c r="K26" s="3" t="str">
         <x:v>查看视觉惯性 odom</x:v>
       </x:c>
-      <x:c r="L22" t="str">
+      <x:c r="L26" s="3" t="str">
         <x:v>rostopic echo -n 1 /vins/imu_propagate</x:v>
       </x:c>
-      <x:c r="M22" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N22" t="str">
+      <x:c r="M26" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N26" s="3" t="str">
         <x:v>当前视觉定位主输出</x:v>
       </x:c>
-      <x:c r="O22" t="str">
+      <x:c r="O26" s="3" t="str">
         <x:v>E011_vins_output</x:v>
       </x:c>
-      <x:c r="P22" t="str">
+      <x:c r="P26" s="14" t="str">
         <x:v>uav/10-knowledge-base/05-传感器与状态回传.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="str">
+    <x:row r="27">
+      <x:c r="A27" s="13" t="str">
         <x:v>I022</x:v>
       </x:c>
-      <x:c r="B23" t="str">
+      <x:c r="B27" s="3" t="str">
         <x:v>state</x:v>
       </x:c>
-      <x:c r="C23" t="str">
+      <x:c r="C27" s="3" t="str">
         <x:v>/drone_0_planning/trajectory</x:v>
       </x:c>
-      <x:c r="D23" t="str">
+      <x:c r="D27" s="3" t="str">
         <x:v>ros_topic</x:v>
       </x:c>
-      <x:c r="E23" t="str">
+      <x:c r="E27" s="3" t="str">
         <x:v>publish</x:v>
       </x:c>
-      <x:c r="F23" t="str">
+      <x:c r="F27" s="3" t="str">
         <x:v>traj_utils/PolyTraj</x:v>
       </x:c>
-      <x:c r="G23" t="str">
+      <x:c r="G27" s="3" t="str">
         <x:v>trajectory</x:v>
       </x:c>
-      <x:c r="H23" t="str">
+      <x:c r="H27" s="3" t="str">
         <x:v>traj_server</x:v>
       </x:c>
-      <x:c r="I23" t="str">
+      <x:c r="I27" s="3" t="str">
         <x:v>operator / px4ctrl</x:v>
       </x:c>
-      <x:c r="J23" t="str">
+      <x:c r="J27" s="3" t="str">
         <x:v>规划链已启动</x:v>
       </x:c>
-      <x:c r="K23" t="str">
+      <x:c r="K27" s="3" t="str">
         <x:v>查看当前规划结果</x:v>
       </x:c>
-      <x:c r="L23" t="str">
+      <x:c r="L27" s="3" t="str">
         <x:v>rostopic echo -n 1 /drone_0_planning/trajectory</x:v>
       </x:c>
-      <x:c r="M23" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N23" t="str">
+      <x:c r="M27" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N27" s="3" t="str">
         <x:v>轨迹有了不等于控制器一定执行</x:v>
       </x:c>
-      <x:c r="O23" t="str">
+      <x:c r="O27" s="3" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
-      <x:c r="P23" t="str">
+      <x:c r="P27" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/diff_planner/plan_manage/launch/exp/run_exp_single_lio.launch</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="str">
+    <x:row r="28">
+      <x:c r="A28" s="13" t="str">
         <x:v>I023</x:v>
       </x:c>
-      <x:c r="B24" t="str">
+      <x:c r="B28" s="3" t="str">
         <x:v>parameter</x:v>
       </x:c>
-      <x:c r="C24" t="str">
+      <x:c r="C28" s="3" t="str">
         <x:v>points.yaml</x:v>
       </x:c>
-      <x:c r="D24" t="str">
+      <x:c r="D28" s="3" t="str">
         <x:v>file</x:v>
       </x:c>
-      <x:c r="E24" t="str">
+      <x:c r="E28" s="3" t="str">
         <x:v>read</x:v>
       </x:c>
-      <x:c r="F24" t="str">
+      <x:c r="F28" s="3" t="str">
         <x:v>yaml</x:v>
       </x:c>
-      <x:c r="G24" t="str">
+      <x:c r="G28" s="3" t="str">
         <x:v>test1 test2 test3 test4 test_back</x:v>
       </x:c>
-      <x:c r="H24" t="str">
+      <x:c r="H28" s="3" t="str">
         <x:v>multipoint config</x:v>
       </x:c>
-      <x:c r="I24" t="str">
+      <x:c r="I28" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="J24" t="str">
+      <x:c r="J28" s="3" t="str">
         <x:v>任务模式与航点格式要匹配</x:v>
       </x:c>
-      <x:c r="K24" t="str">
+      <x:c r="K28" s="3" t="str">
         <x:v>定义任务点和返程点</x:v>
       </x:c>
-      <x:c r="L24" t="str">
+      <x:c r="L28" s="3" t="str">
         <x:v>src/user_command/multipoint/config/points.yaml</x:v>
       </x:c>
-      <x:c r="M24" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N24" t="str">
+      <x:c r="M28" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N28" s="3" t="str">
         <x:v>数组长度错会直接读取失败</x:v>
       </x:c>
-      <x:c r="O24" t="str">
+      <x:c r="O28" s="3" t="str">
         <x:v>E015_points_yaml</x:v>
       </x:c>
-      <x:c r="P24" t="str">
+      <x:c r="P28" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/config/points.yaml</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
+    <x:row r="29">
+      <x:c r="A29" s="13" t="str">
         <x:v>I024</x:v>
       </x:c>
-      <x:c r="B25" t="str">
+      <x:c r="B29" s="3" t="str">
         <x:v>parameter</x:v>
       </x:c>
-      <x:c r="C25" t="str">
+      <x:c r="C29" s="3" t="str">
         <x:v>ctrl_param_fpv.yaml</x:v>
       </x:c>
-      <x:c r="D25" t="str">
+      <x:c r="D29" s="3" t="str">
         <x:v>file</x:v>
       </x:c>
-      <x:c r="E25" t="str">
+      <x:c r="E29" s="3" t="str">
         <x:v>read</x:v>
       </x:c>
-      <x:c r="F25" t="str">
+      <x:c r="F29" s="3" t="str">
         <x:v>yaml</x:v>
       </x:c>
-      <x:c r="G25" t="str">
+      <x:c r="G29" s="3" t="str">
         <x:v>low_voltage takeoff_height takeoff_land_speed</x:v>
       </x:c>
-      <x:c r="H25" t="str">
+      <x:c r="H29" s="3" t="str">
         <x:v>px4ctrl config</x:v>
       </x:c>
-      <x:c r="I25" t="str">
+      <x:c r="I29" s="3" t="str">
         <x:v>px4ctrl</x:v>
       </x:c>
-      <x:c r="J25" t="str">
+      <x:c r="J29" s="3" t="str">
         <x:v>px4ctrl 启动前读取</x:v>
       </x:c>
-      <x:c r="K25" t="str">
+      <x:c r="K29" s="3" t="str">
         <x:v>控制起飞高度和电池阈值</x:v>
       </x:c>
-      <x:c r="L25" t="str">
+      <x:c r="L29" s="3" t="str">
         <x:v>src/realflight_modules/px4ctrl/config/ctrl_param_fpv.yaml</x:v>
       </x:c>
-      <x:c r="M25" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N25" t="str">
+      <x:c r="M29" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N29" s="3" t="str">
         <x:v>改前必须确认起飞高度范围无障碍</x:v>
       </x:c>
-      <x:c r="O25" t="str">
+      <x:c r="O29" s="3" t="str">
         <x:v>E014_ctrl_params</x:v>
       </x:c>
-      <x:c r="P25" t="str">
+      <x:c r="P29" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/realflight_modules/px4ctrl/config/ctrl_param_fpv.yaml</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
+    <x:row r="30">
+      <x:c r="A30" s="13" t="str">
         <x:v>I025</x:v>
       </x:c>
-      <x:c r="B26" t="str">
+      <x:c r="B30" s="3" t="str">
         <x:v>parameter</x:v>
       </x:c>
-      <x:c r="C26" t="str">
+      <x:c r="C30" s="3" t="str">
         <x:v>multipointplan_exp_lio.launch</x:v>
       </x:c>
-      <x:c r="D26" t="str">
+      <x:c r="D30" s="3" t="str">
         <x:v>file</x:v>
       </x:c>
-      <x:c r="E26" t="str">
+      <x:c r="E30" s="3" t="str">
         <x:v>read</x:v>
       </x:c>
-      <x:c r="F26" t="str">
+      <x:c r="F30" s="3" t="str">
         <x:v>roslaunch args</x:v>
       </x:c>
-      <x:c r="G26" t="str">
+      <x:c r="G30" s="3" t="str">
         <x:v>fligt_type next_distance start_plan back_plan</x:v>
       </x:c>
-      <x:c r="H26" t="str">
+      <x:c r="H30" s="3" t="str">
         <x:v>launch config</x:v>
       </x:c>
-      <x:c r="I26" t="str">
+      <x:c r="I30" s="3" t="str">
         <x:v>multipoint</x:v>
       </x:c>
-      <x:c r="J26" t="str">
+      <x:c r="J30" s="3" t="str">
         <x:v>LIO 任务链启动前读取</x:v>
       </x:c>
-      <x:c r="K26" t="str">
+      <x:c r="K30" s="3" t="str">
         <x:v>选择航点模式和触发行为</x:v>
       </x:c>
-      <x:c r="L26" t="str">
+      <x:c r="L30" s="3" t="str">
         <x:v>roslaunch multipoint multipointplan_exp_lio.launch</x:v>
       </x:c>
-      <x:c r="M26" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N26" t="str">
+      <x:c r="M30" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N30" s="3" t="str">
         <x:v>fligt_type 拼写就是源码现状 不要擅自改名</x:v>
       </x:c>
-      <x:c r="O26" t="str">
+      <x:c r="O30" s="3" t="str">
         <x:v>E015_points_yaml</x:v>
       </x:c>
-      <x:c r="P26" t="str">
+      <x:c r="P30" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/launch/multipointplan_exp_lio.launch</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
+    <x:row r="31">
+      <x:c r="A31" s="13" t="str">
         <x:v>I026</x:v>
       </x:c>
-      <x:c r="B27" t="str">
+      <x:c r="B31" s="3" t="str">
         <x:v>parameter</x:v>
       </x:c>
-      <x:c r="C27" t="str">
+      <x:c r="C31" s="3" t="str">
         <x:v>run_exp_single_lio.launch</x:v>
       </x:c>
-      <x:c r="D27" t="str">
+      <x:c r="D31" s="3" t="str">
         <x:v>file</x:v>
       </x:c>
-      <x:c r="E27" t="str">
+      <x:c r="E31" s="3" t="str">
         <x:v>read</x:v>
       </x:c>
-      <x:c r="F27" t="str">
+      <x:c r="F31" s="3" t="str">
         <x:v>roslaunch args</x:v>
       </x:c>
-      <x:c r="G27" t="str">
+      <x:c r="G31" s="3" t="str">
         <x:v>max_vel max_acc map_resolution flight_type</x:v>
       </x:c>
-      <x:c r="H27" t="str">
+      <x:c r="H31" s="3" t="str">
         <x:v>launch config</x:v>
       </x:c>
-      <x:c r="I27" t="str">
+      <x:c r="I31" s="3" t="str">
         <x:v>planner</x:v>
       </x:c>
-      <x:c r="J27" t="str">
+      <x:c r="J31" s="3" t="str">
         <x:v>LIO 规划链启动前读取</x:v>
       </x:c>
-      <x:c r="K27" t="str">
+      <x:c r="K31" s="3" t="str">
         <x:v>配置 LIO 规划参数</x:v>
       </x:c>
-      <x:c r="L27" t="str">
+      <x:c r="L31" s="3" t="str">
         <x:v>roslaunch diff_planner run_exp_single_lio.launch</x:v>
       </x:c>
-      <x:c r="M27" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N27" t="str">
+      <x:c r="M31" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N31" s="3" t="str">
         <x:v>是规划参数不是飞控参数</x:v>
       </x:c>
-      <x:c r="O27" t="str">
+      <x:c r="O31" s="3" t="str">
         <x:v>E006_run_single_lio_script</x:v>
       </x:c>
-      <x:c r="P27" t="str">
+      <x:c r="P31" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/diff_planner/plan_manage/launch/exp/run_exp_single_lio.launch</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
-      <x:c r="A28" t="str">
+    <x:row r="32">
+      <x:c r="A32" s="13" t="str">
         <x:v>I027</x:v>
       </x:c>
-      <x:c r="B28" t="str">
+      <x:c r="B32" s="3" t="str">
         <x:v>parameter</x:v>
       </x:c>
-      <x:c r="C28" t="str">
+      <x:c r="C32" s="3" t="str">
         <x:v>run_exp_single_vio.launch</x:v>
       </x:c>
-      <x:c r="D28" t="str">
+      <x:c r="D32" s="3" t="str">
         <x:v>file</x:v>
       </x:c>
-      <x:c r="E28" t="str">
+      <x:c r="E32" s="3" t="str">
         <x:v>read</x:v>
       </x:c>
-      <x:c r="F28" t="str">
+      <x:c r="F32" s="3" t="str">
         <x:v>roslaunch args</x:v>
       </x:c>
-      <x:c r="G28" t="str">
+      <x:c r="G32" s="3" t="str">
         <x:v>cx cy fx fy max_vel max_acc</x:v>
       </x:c>
-      <x:c r="H28" t="str">
+      <x:c r="H32" s="3" t="str">
         <x:v>launch config</x:v>
       </x:c>
-      <x:c r="I28" t="str">
+      <x:c r="I32" s="3" t="str">
         <x:v>planner</x:v>
       </x:c>
-      <x:c r="J28" t="str">
+      <x:c r="J32" s="3" t="str">
         <x:v>VIO 规划链启动前读取</x:v>
       </x:c>
-      <x:c r="K28" t="str">
+      <x:c r="K32" s="3" t="str">
         <x:v>配置 VIO 规划参数</x:v>
       </x:c>
-      <x:c r="L28" t="str">
+      <x:c r="L32" s="3" t="str">
         <x:v>roslaunch diff_planner run_exp_single_vio.launch</x:v>
       </x:c>
-      <x:c r="M28" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N28" t="str">
+      <x:c r="M32" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N32" s="3" t="str">
         <x:v>视觉内参错误会直接破坏 VIO 规划</x:v>
       </x:c>
-      <x:c r="O28" t="str">
+      <x:c r="O32" s="3" t="str">
         <x:v>E007_run_single_vio_script</x:v>
       </x:c>
-      <x:c r="P28" t="str">
+      <x:c r="P32" s="14" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/diff_planner/plan_manage/launch/exp/run_exp_single_vio.launch</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
-      <x:c r="A29" t="str">
+    <x:row r="33">
+      <x:c r="A33" s="13" t="str">
         <x:v>I028</x:v>
       </x:c>
-      <x:c r="B29" t="str">
+      <x:c r="B33" s="3" t="str">
         <x:v>rc</x:v>
       </x:c>
-      <x:c r="C29" t="str">
+      <x:c r="C33" s="3" t="str">
         <x:v>RC Channel 5</x:v>
       </x:c>
-      <x:c r="D29" t="str">
+      <x:c r="D33" s="3" t="str">
         <x:v>physical_input</x:v>
       </x:c>
-      <x:c r="E29" t="str">
+      <x:c r="E33" s="3" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F29" t="str">
+      <x:c r="F33" s="3" t="str">
         <x:v>remote control</x:v>
       </x:c>
-      <x:c r="G29" t="str">
+      <x:c r="G33" s="3" t="str">
         <x:v>光流 / 姿态 / onboard</x:v>
       </x:c>
-      <x:c r="H29" t="str">
+      <x:c r="H33" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I29" t="str">
+      <x:c r="I33" s="3" t="str">
         <x:v>PX4 / px4ctrl</x:v>
       </x:c>
-      <x:c r="J29" t="str">
+      <x:c r="J33" s="3" t="str">
         <x:v>遥控器在线</x:v>
       </x:c>
-      <x:c r="K29" t="str">
+      <x:c r="K33" s="3" t="str">
         <x:v>切换飞行模式</x:v>
       </x:c>
-      <x:c r="L29" t="str">
+      <x:c r="L33" s="3" t="str">
         <x:v>上=光流 中=姿态 下=onboard</x:v>
       </x:c>
-      <x:c r="M29" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N29" t="str">
+      <x:c r="M33" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N33" s="3" t="str">
         <x:v>软件控制会被它打断</x:v>
       </x:c>
-      <x:c r="O29" t="str">
+      <x:c r="O33" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P29" t="str">
+      <x:c r="P33" s="14" t="str">
         <x:v>uav/10-knowledge-base/01-硬件与系统.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
-      <x:c r="A30" t="str">
+    <x:row r="34">
+      <x:c r="A34" s="13" t="str">
         <x:v>I029</x:v>
       </x:c>
-      <x:c r="B30" t="str">
+      <x:c r="B34" s="3" t="str">
         <x:v>rc</x:v>
       </x:c>
-      <x:c r="C30" t="str">
+      <x:c r="C34" s="3" t="str">
         <x:v>RC Channel 6</x:v>
       </x:c>
-      <x:c r="D30" t="str">
+      <x:c r="D34" s="3" t="str">
         <x:v>physical_input</x:v>
       </x:c>
-      <x:c r="E30" t="str">
+      <x:c r="E34" s="3" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F30" t="str">
+      <x:c r="F34" s="3" t="str">
         <x:v>remote control</x:v>
       </x:c>
-      <x:c r="G30" t="str">
+      <x:c r="G34" s="3" t="str">
         <x:v>悬停 / 轨迹</x:v>
       </x:c>
-      <x:c r="H30" t="str">
+      <x:c r="H34" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I30" t="str">
+      <x:c r="I34" s="3" t="str">
         <x:v>PX4 / px4ctrl</x:v>
       </x:c>
-      <x:c r="J30" t="str">
+      <x:c r="J34" s="3" t="str">
         <x:v>遥控器在线</x:v>
       </x:c>
-      <x:c r="K30" t="str">
+      <x:c r="K34" s="3" t="str">
         <x:v>切换悬停与轨迹控制</x:v>
       </x:c>
-      <x:c r="L30" t="str">
+      <x:c r="L34" s="3" t="str">
         <x:v>上=悬停 下=轨迹</x:v>
       </x:c>
-      <x:c r="M30" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N30" t="str">
+      <x:c r="M34" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N34" s="3" t="str">
         <x:v>异常时上拨 6 通是重要兜底</x:v>
       </x:c>
-      <x:c r="O30" t="str">
+      <x:c r="O34" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P30" t="str">
+      <x:c r="P34" s="14" t="str">
         <x:v>uav/10-knowledge-base/01-硬件与系统.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
-      <x:c r="A31" t="str">
+    <x:row r="35">
+      <x:c r="A35" s="13" t="str">
         <x:v>I030</x:v>
       </x:c>
-      <x:c r="B31" t="str">
+      <x:c r="B35" s="3" t="str">
         <x:v>rc</x:v>
       </x:c>
-      <x:c r="C31" t="str">
+      <x:c r="C35" s="3" t="str">
         <x:v>RC Channel 7</x:v>
       </x:c>
-      <x:c r="D31" t="str">
+      <x:c r="D35" s="3" t="str">
         <x:v>physical_input</x:v>
       </x:c>
-      <x:c r="E31" t="str">
+      <x:c r="E35" s="3" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F31" t="str">
+      <x:c r="F35" s="3" t="str">
         <x:v>remote control</x:v>
       </x:c>
-      <x:c r="G31" t="str">
+      <x:c r="G35" s="3" t="str">
         <x:v>解锁 / 锁桨 / 急停</x:v>
       </x:c>
-      <x:c r="H31" t="str">
+      <x:c r="H35" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I31" t="str">
+      <x:c r="I35" s="3" t="str">
         <x:v>PX4</x:v>
       </x:c>
-      <x:c r="J31" t="str">
+      <x:c r="J35" s="3" t="str">
         <x:v>遥控器在线</x:v>
       </x:c>
-      <x:c r="K31" t="str">
+      <x:c r="K35" s="3" t="str">
         <x:v>电机安全控制</x:v>
       </x:c>
-      <x:c r="L31" t="str">
+      <x:c r="L35" s="3" t="str">
         <x:v>上=解锁 下=急停</x:v>
       </x:c>
-      <x:c r="M31" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N31" t="str">
+      <x:c r="M35" s="3" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N35" s="3" t="str">
         <x:v>最高安全优先级</x:v>
       </x:c>
-      <x:c r="O31" t="str">
+      <x:c r="O35" s="3" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P31" t="str">
+      <x:c r="P35" s="14" t="str">
         <x:v>uav/10-knowledge-base/01-硬件与系统.md</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
-      <x:c r="A32" t="str">
+    <x:row r="36">
+      <x:c r="A36" s="15" t="str">
         <x:v>I031</x:v>
       </x:c>
-      <x:c r="B32" t="str">
+      <x:c r="B36" s="16" t="str">
         <x:v>rc</x:v>
       </x:c>
-      <x:c r="C32" t="str">
+      <x:c r="C36" s="16" t="str">
         <x:v>RC Channel 8</x:v>
       </x:c>
-      <x:c r="D32" t="str">
+      <x:c r="D36" s="16" t="str">
         <x:v>physical_input</x:v>
       </x:c>
-      <x:c r="E32" t="str">
+      <x:c r="E36" s="16" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F32" t="str">
+      <x:c r="F36" s="16" t="str">
         <x:v>remote control</x:v>
       </x:c>
-      <x:c r="G32" t="str">
+      <x:c r="G36" s="16" t="str">
         <x:v>下-&gt;中 takeoff 中-&gt;上 start 上-&gt;中 back 中-&gt;下 land</x:v>
       </x:c>
-      <x:c r="H32" t="str">
+      <x:c r="H36" s="16" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I32" t="str">
+      <x:c r="I36" s="16" t="str">
         <x:v>multipoint / PX4</x:v>
       </x:c>
-      <x:c r="J32" t="str">
+      <x:c r="J36" s="16" t="str">
         <x:v>遥控器在线且 mavros/rc/in 正常</x:v>
       </x:c>
-      <x:c r="K32" t="str">
+      <x:c r="K36" s="16" t="str">
         <x:v>任务动作触发</x:v>
       </x:c>
-      <x:c r="L32" t="str">
+      <x:c r="L36" s="16" t="str">
         <x:v>下/中/上 档位切换</x:v>
       </x:c>
-      <x:c r="M32" t="str">
-        <x:v>onboard-active</x:v>
-      </x:c>
-      <x:c r="N32" t="str">
+      <x:c r="M36" s="16" t="str">
+        <x:v>onboard-active</x:v>
+      </x:c>
+      <x:c r="N36" s="16" t="str">
         <x:v>脚本与 RC 触发方式不要混用</x:v>
       </x:c>
-      <x:c r="O32" t="str">
+      <x:c r="O36" s="16" t="str">
         <x:v>E009_rc_mapping</x:v>
       </x:c>
-      <x:c r="P32" t="str">
+      <x:c r="P36" s="17" t="str">
         <x:v>uav/03-drone-code/snapshot_20260421_174511/Diff-planner/src/user_command/multipoint/src/multipointplan.cpp</x:v>
       </x:c>
     </x:row>
